--- a/compare/output/dscale_per_capita_co2_downscaled_SSP126.xlsx
+++ b/compare/output/dscale_per_capita_co2_downscaled_SSP126.xlsx
@@ -529,55 +529,55 @@
         <v>0.01464644522987098</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01964611738026903</v>
+        <v>0.01964593089069286</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01974139819549332</v>
+        <v>0.0197412283755534</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02006321942850205</v>
+        <v>0.0200629828878616</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01972284005700358</v>
+        <v>0.01972261808043543</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01840878513813882</v>
+        <v>0.01840857524856173</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01753252082700822</v>
+        <v>0.01753232064751394</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01733853411439235</v>
+        <v>0.01733834146115918</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01840242871148075</v>
+        <v>0.0184022416188749</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02020238174496382</v>
+        <v>0.02020219850562209</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02311182739533843</v>
+        <v>0.02311164644778849</v>
       </c>
       <c r="P2" t="n">
-        <v>0.02646835740791413</v>
+        <v>0.02646823739504875</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0304216137703077</v>
+        <v>0.03042143341106816</v>
       </c>
       <c r="R2" t="n">
-        <v>0.03414036536541089</v>
+        <v>0.03414018346487774</v>
       </c>
       <c r="S2" t="n">
-        <v>0.03698812250424636</v>
+        <v>0.03698799946601408</v>
       </c>
       <c r="T2" t="n">
-        <v>0.03894724687593543</v>
+        <v>0.03894712136739049</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04125126088478086</v>
+        <v>0.04125106789221237</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0439230818173624</v>
+        <v>0.04392288298701505</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         <v>0.1313054140728165</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1351481687661018</v>
+        <v>0.1351492476125129</v>
       </c>
       <c r="T3" t="n">
         <v>0.1360439168079979</v>
@@ -681,7 +681,7 @@
         <v>0.2734443014841635</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2920507040672234</v>
+        <v>0.2920516719237406</v>
       </c>
       <c r="G4" t="n">
         <v>0.2413864486752627</v>
@@ -702,13 +702,13 @@
         <v>0.1694656405658343</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1721909993823632</v>
+        <v>0.1721917666330355</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1778442962803373</v>
+        <v>0.1778450602753896</v>
       </c>
       <c r="O4" t="n">
-        <v>0.189813653001016</v>
+        <v>0.1898144180979079</v>
       </c>
       <c r="P4" t="n">
         <v>0.2030136420581586</v>
@@ -729,7 +729,7 @@
         <v>0.2674896481133978</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2706321626287544</v>
+        <v>0.2706330548207364</v>
       </c>
     </row>
     <row r="5">
@@ -766,7 +766,7 @@
         <v>0.06998744110956756</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07677339813706248</v>
+        <v>0.07677328243815545</v>
       </c>
       <c r="J5" t="n">
         <v>0.07550419634608288</v>
@@ -778,7 +778,7 @@
         <v>0.07109223633288646</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07263126882470888</v>
+        <v>0.07263117347955465</v>
       </c>
       <c r="N5" t="n">
         <v>0.0751261192120747</v>
@@ -805,7 +805,7 @@
         <v>0.1070740308851509</v>
       </c>
       <c r="V5" t="n">
-        <v>0.108596594222695</v>
+        <v>0.1085966910988272</v>
       </c>
     </row>
     <row r="6">
@@ -830,58 +830,58 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.04779996761212667</v>
+        <v>0.04779993491911859</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06363638798348652</v>
+        <v>0.06363631854909904</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0576122706020859</v>
+        <v>0.05761217013417946</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05364614585983671</v>
+        <v>0.05364602632778761</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05041599030558075</v>
+        <v>0.05041585315084762</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04634636311723574</v>
+        <v>0.04634623228580972</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04417383833098862</v>
+        <v>0.04417371992359763</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0433166699400892</v>
+        <v>0.04331655525083258</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0448974861829203</v>
+        <v>0.04489737431788547</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0473640721835652</v>
+        <v>0.04736396232348575</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05162389805270352</v>
+        <v>0.05162379629535409</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0563611562944273</v>
+        <v>0.0563610551796708</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.06337489659149395</v>
+        <v>0.06337480227754709</v>
       </c>
       <c r="R6" t="n">
-        <v>0.07083241029862994</v>
+        <v>0.07083232905352158</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07677627392348589</v>
+        <v>0.07677619865474228</v>
       </c>
       <c r="T6" t="n">
-        <v>0.08018921980469562</v>
+        <v>0.0801891572205112</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0815822848193644</v>
+        <v>0.08158222089641286</v>
       </c>
       <c r="V6" t="n">
-        <v>0.08198413004963732</v>
+        <v>0.08198407174710108</v>
       </c>
     </row>
     <row r="7">
@@ -906,58 +906,58 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.1274078765364971</v>
+        <v>0.1274079207785</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1760480722117047</v>
+        <v>0.176048213011334</v>
       </c>
       <c r="G7" t="n">
-        <v>0.190697661497569</v>
+        <v>0.1906978652192304</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2136330847517502</v>
+        <v>0.2136333607362992</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2292855298109487</v>
+        <v>0.2292858698459398</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2290129635799166</v>
+        <v>0.229013316530824</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2261752700776958</v>
+        <v>0.2261756375103469</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2217216748929531</v>
+        <v>0.2217220444859146</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2228814927204054</v>
+        <v>0.2228818529489067</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2229029014387363</v>
+        <v>0.2229032548798321</v>
       </c>
       <c r="O7" t="n">
-        <v>0.226522793778947</v>
+        <v>0.2265231289303201</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2286432733848089</v>
+        <v>0.2286436056568653</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2331430550089501</v>
+        <v>0.2331433729269264</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2350864140007292</v>
+        <v>0.235086719144282</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2319774927382367</v>
+        <v>0.2319777997331013</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2250000505747108</v>
+        <v>0.2250003337930912</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2167110737835219</v>
+        <v>0.2167113475353982</v>
       </c>
       <c r="V7" t="n">
-        <v>0.20932694247868</v>
+        <v>0.2093272076091898</v>
       </c>
     </row>
     <row r="8">
@@ -982,58 +982,58 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04755070629300511</v>
+        <v>0.04755066344322018</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06239300247365473</v>
+        <v>0.06239296389513432</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06156976799485114</v>
+        <v>0.06156969753974285</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06188061008776424</v>
+        <v>0.06188051218759239</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06072825632970469</v>
+        <v>0.06072813411546373</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05683721958355322</v>
+        <v>0.05683710385245674</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05411896635166106</v>
+        <v>0.05411888324403419</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05279363652483884</v>
+        <v>0.05279355616710765</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05409252594762105</v>
+        <v>0.05409242158837897</v>
       </c>
       <c r="N8" t="n">
-        <v>0.05614576935660332</v>
+        <v>0.05614569261650235</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06002990951941369</v>
+        <v>0.06002980857604746</v>
       </c>
       <c r="P8" t="n">
-        <v>0.06439548966015136</v>
+        <v>0.06439541450953074</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.07014223357068533</v>
+        <v>0.07014213349605466</v>
       </c>
       <c r="R8" t="n">
-        <v>0.07584405325572467</v>
+        <v>0.07584397783265784</v>
       </c>
       <c r="S8" t="n">
-        <v>0.08016085259297145</v>
+        <v>0.08016077633060043</v>
       </c>
       <c r="T8" t="n">
-        <v>0.08275987386573183</v>
+        <v>0.08275982213319627</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08406227606183435</v>
+        <v>0.08406222309789274</v>
       </c>
       <c r="V8" t="n">
-        <v>0.08474210239109264</v>
+        <v>0.08474207512010823</v>
       </c>
     </row>
     <row r="9">
@@ -1058,58 +1058,58 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9770450427956572</v>
+        <v>0.9770457948500818</v>
       </c>
       <c r="F9" t="n">
-        <v>1.074086134229365</v>
+        <v>1.074087607642002</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8658484970590538</v>
+        <v>0.8658499465150727</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7439793275723454</v>
+        <v>0.7439807619622741</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6491459366033689</v>
+        <v>0.6491473626567946</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5598664094402476</v>
+        <v>0.5598671218472429</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4991480149571503</v>
+        <v>0.4991494462633962</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4613850493204433</v>
+        <v>0.4613857721761281</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4489649349191689</v>
+        <v>0.448966402108057</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4401393814704281</v>
+        <v>0.4401401290646699</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4405681718141767</v>
+        <v>0.4405697028619109</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4499474108503697</v>
+        <v>0.4499481981130887</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4704701685700163</v>
+        <v>0.4704709815041232</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4895558409427214</v>
+        <v>0.4895566836213609</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4970683113701469</v>
+        <v>0.4970691882023974</v>
       </c>
       <c r="T9" t="n">
-        <v>0.496425723033045</v>
+        <v>0.4964266418703116</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4915135906665012</v>
+        <v>0.4915145603202185</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4868384072048254</v>
+        <v>0.486839436700918</v>
       </c>
     </row>
     <row r="10">
@@ -1137,55 +1137,55 @@
         <v>0.02983536287061659</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03654304337717426</v>
+        <v>0.03654296861858842</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03222593518049213</v>
+        <v>0.03222579856305783</v>
       </c>
       <c r="H10" t="n">
-        <v>0.02994574692988586</v>
+        <v>0.02994562045111184</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02782032075488358</v>
+        <v>0.02782014416015964</v>
       </c>
       <c r="J10" t="n">
-        <v>0.02527511879879137</v>
+        <v>0.02527495326401473</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02390251448089316</v>
+        <v>0.02390230544598642</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02356833793580429</v>
+        <v>0.02356818780083295</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02467061877384722</v>
+        <v>0.02467047367731208</v>
       </c>
       <c r="N10" t="n">
-        <v>0.02635914131153159</v>
+        <v>0.02635900009226326</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02893996887001851</v>
+        <v>0.02893978466894462</v>
       </c>
       <c r="P10" t="n">
-        <v>0.03159654220964507</v>
+        <v>0.0315964063329414</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.03459912643562794</v>
+        <v>0.03459894720617123</v>
       </c>
       <c r="R10" t="n">
-        <v>0.03725576559917116</v>
+        <v>0.03725558727707509</v>
       </c>
       <c r="S10" t="n">
-        <v>0.03974342116113492</v>
+        <v>0.03974328743810295</v>
       </c>
       <c r="T10" t="n">
-        <v>0.04186929519654878</v>
+        <v>0.04186911611698194</v>
       </c>
       <c r="U10" t="n">
-        <v>0.04354766222591595</v>
+        <v>0.04354748155458646</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0447858932607525</v>
+        <v>0.04478571009916368</v>
       </c>
     </row>
     <row r="11">
@@ -1210,58 +1210,58 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.1447735738200035</v>
+        <v>0.144773656542962</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1865374398839458</v>
+        <v>0.1865375909174492</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1817593127376519</v>
+        <v>0.1817594875459571</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1836765510550196</v>
+        <v>0.1836767642184519</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1805372041468031</v>
+        <v>0.1805374060904014</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1619630448409786</v>
+        <v>0.1619632233036565</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1454820740790184</v>
+        <v>0.1454822179340632</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1343642255707452</v>
+        <v>0.1343643380148499</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1330896192819865</v>
+        <v>0.1330897300254447</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1353481499129816</v>
+        <v>0.1353482597067655</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1422001324110658</v>
+        <v>0.1422002419548638</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1488155521001321</v>
+        <v>0.1488156758245165</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1565758410688162</v>
+        <v>0.1565759660811091</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1616912564848077</v>
+        <v>0.161691397735247</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1622119021530997</v>
+        <v>0.1622120322663517</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1589837229056241</v>
+        <v>0.1589838419968744</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1540661416167464</v>
+        <v>0.1540662495079391</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1497440410009095</v>
+        <v>0.1497441532601115</v>
       </c>
     </row>
     <row r="12">
@@ -1289,52 +1289,52 @@
         <v>0.0260483621109368</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03594758374264368</v>
+        <v>0.03594749174556183</v>
       </c>
       <c r="G12" t="n">
-        <v>0.03824679047455825</v>
+        <v>0.03824661648117522</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0415924325167992</v>
+        <v>0.04159226647583025</v>
       </c>
       <c r="I12" t="n">
-        <v>0.04335316477935187</v>
+        <v>0.0433530050630081</v>
       </c>
       <c r="J12" t="n">
-        <v>0.04298874565713535</v>
+        <v>0.04298859024260985</v>
       </c>
       <c r="K12" t="n">
-        <v>0.04302646415374151</v>
+        <v>0.04302631095150843</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04391455485943873</v>
+        <v>0.04391447857730774</v>
       </c>
       <c r="M12" t="n">
-        <v>0.04683844427250512</v>
+        <v>0.04683836766587252</v>
       </c>
       <c r="N12" t="n">
-        <v>0.05018650746416321</v>
+        <v>0.05018643017138899</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0550999370561325</v>
+        <v>0.05509985896200408</v>
       </c>
       <c r="P12" t="n">
-        <v>0.06053856015561106</v>
+        <v>0.06053848121331157</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.06754847323023415</v>
+        <v>0.06754839323810538</v>
       </c>
       <c r="R12" t="n">
-        <v>0.07442074957902958</v>
+        <v>0.07442066838897829</v>
       </c>
       <c r="S12" t="n">
         <v>0.07973948001623918</v>
       </c>
       <c r="T12" t="n">
-        <v>0.08323720292849963</v>
+        <v>0.08323711895959164</v>
       </c>
       <c r="U12" t="n">
-        <v>0.08546104295449317</v>
+        <v>0.08546095742014727</v>
       </c>
       <c r="V12" t="n">
         <v>0.08725186772324819</v>
@@ -1362,58 +1362,58 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.04535621756271209</v>
+        <v>0.04535619157129549</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05827071579091253</v>
+        <v>0.05827064721696044</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05497394425601927</v>
+        <v>0.05497384272167283</v>
       </c>
       <c r="H13" t="n">
-        <v>0.05413494260671649</v>
+        <v>0.05413481494450342</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05295526021647479</v>
+        <v>0.05295512819349157</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0500325056005353</v>
+        <v>0.05003236972018007</v>
       </c>
       <c r="K13" t="n">
-        <v>0.04835592159448392</v>
+        <v>0.04835580974718456</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04772553956288166</v>
+        <v>0.04772542171722594</v>
       </c>
       <c r="M13" t="n">
-        <v>0.04906269282989247</v>
+        <v>0.04906259384362323</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0504821220229945</v>
+        <v>0.05048201592608866</v>
       </c>
       <c r="O13" t="n">
-        <v>0.05284558769536016</v>
+        <v>0.05284548586498174</v>
       </c>
       <c r="P13" t="n">
-        <v>0.05485339244811702</v>
+        <v>0.05485329398182793</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.05735397783499065</v>
+        <v>0.05735386064886808</v>
       </c>
       <c r="R13" t="n">
-        <v>0.05921496203946276</v>
+        <v>0.05921484721472237</v>
       </c>
       <c r="S13" t="n">
-        <v>0.06033958206660902</v>
+        <v>0.06033945863009956</v>
       </c>
       <c r="T13" t="n">
-        <v>0.06071272704294056</v>
+        <v>0.06071261492926137</v>
       </c>
       <c r="U13" t="n">
-        <v>0.06059594236709671</v>
+        <v>0.06059583067384942</v>
       </c>
       <c r="V13" t="n">
-        <v>0.06028820279571009</v>
+        <v>0.06028809093232336</v>
       </c>
     </row>
     <row r="14">
@@ -1438,58 +1438,58 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.17126099946923</v>
+        <v>1.171274869757989</v>
       </c>
       <c r="F14" t="n">
-        <v>1.278266756905851</v>
+        <v>1.27829083514963</v>
       </c>
       <c r="G14" t="n">
-        <v>1.274607427528315</v>
+        <v>1.274638788182076</v>
       </c>
       <c r="H14" t="n">
-        <v>1.297599947613697</v>
+        <v>1.29763739636344</v>
       </c>
       <c r="I14" t="n">
-        <v>1.288144315936734</v>
+        <v>1.288185008317131</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2654988311368</v>
+        <v>1.265540764550917</v>
       </c>
       <c r="K14" t="n">
-        <v>1.233243204367137</v>
+        <v>1.233284702225838</v>
       </c>
       <c r="L14" t="n">
-        <v>1.193052773105701</v>
+        <v>1.193092818428928</v>
       </c>
       <c r="M14" t="n">
-        <v>1.14653749042651</v>
+        <v>1.146575872470319</v>
       </c>
       <c r="N14" t="n">
-        <v>1.083159056360792</v>
+        <v>1.083195707599224</v>
       </c>
       <c r="O14" t="n">
-        <v>1.000589693432276</v>
+        <v>1.000624698065242</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9324963747524088</v>
+        <v>0.9325307478129967</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8459880018651724</v>
+        <v>0.8460214646926767</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7603444883097253</v>
+        <v>0.7603772932150034</v>
       </c>
       <c r="S14" t="n">
-        <v>0.677687386647199</v>
+        <v>0.6777200220791543</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6016084067186255</v>
+        <v>0.6016417041626565</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5335440502895933</v>
+        <v>0.5335790839605372</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4694920575850764</v>
+        <v>0.4695299371731293</v>
       </c>
     </row>
     <row r="15">
@@ -1514,58 +1514,58 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.7351407245680917</v>
+        <v>0.7351369448880398</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8719541695138576</v>
+        <v>0.8719499823894473</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8988411502795081</v>
+        <v>0.8988386080950069</v>
       </c>
       <c r="H15" t="n">
-        <v>0.923021365715507</v>
+        <v>0.9230203410043535</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9123505903244475</v>
+        <v>0.912350175598666</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8871851084088699</v>
+        <v>0.8871844760734352</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8550572358418255</v>
+        <v>0.8550557100313958</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8195396522245745</v>
+        <v>0.819536863150308</v>
       </c>
       <c r="M15" t="n">
-        <v>0.782052156476459</v>
+        <v>0.782047965048588</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7350094474201747</v>
+        <v>0.7350039850138927</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6765585635951612</v>
+        <v>0.6765521378881136</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6294605229821214</v>
+        <v>0.6294532234146031</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.5709734046087186</v>
+        <v>0.5709655037430351</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5133920807226093</v>
+        <v>0.5133836263688001</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4565899651774302</v>
+        <v>0.4565808190988114</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4030286343718469</v>
+        <v>0.4030187082778805</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3544360510394174</v>
+        <v>0.3544253092491787</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3090033659063542</v>
+        <v>0.308991700239012</v>
       </c>
     </row>
     <row r="16">
@@ -1590,58 +1590,58 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2.133758759339717</v>
+        <v>2.133818393075406</v>
       </c>
       <c r="F16" t="n">
-        <v>1.980585458107704</v>
+        <v>1.980674576178944</v>
       </c>
       <c r="G16" t="n">
-        <v>1.628606651691741</v>
+        <v>1.628688691854035</v>
       </c>
       <c r="H16" t="n">
-        <v>1.420338123963587</v>
+        <v>1.420405396483814</v>
       </c>
       <c r="I16" t="n">
-        <v>1.262502076192535</v>
+        <v>1.262554367732796</v>
       </c>
       <c r="J16" t="n">
-        <v>1.152038731785707</v>
+        <v>1.152079855085733</v>
       </c>
       <c r="K16" t="n">
-        <v>1.073972671781761</v>
+        <v>1.074006387308785</v>
       </c>
       <c r="L16" t="n">
-        <v>1.016397345485223</v>
+        <v>1.016426580728649</v>
       </c>
       <c r="M16" t="n">
-        <v>0.973198696998003</v>
+        <v>0.9732261636929467</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9247658031112614</v>
+        <v>0.9247927465900434</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8620715782260934</v>
+        <v>0.8620983868908356</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8153413243803918</v>
+        <v>0.8153696176509524</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.7564848836143095</v>
+        <v>0.7565154092446112</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7004955128380482</v>
+        <v>0.7005296770750921</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6457737697294911</v>
+        <v>0.6458128070351609</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5906489996006071</v>
+        <v>0.5906933060672945</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5351447223357672</v>
+        <v>0.5351944811769694</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4764464516656982</v>
+        <v>0.4765016054022463</v>
       </c>
     </row>
     <row r="17">
@@ -1666,58 +1666,58 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.4955096906332869</v>
+        <v>0.4954916080010826</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5691475164224563</v>
+        <v>0.5691112339104512</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5747632523340344</v>
+        <v>0.5747153954020444</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5811259557274974</v>
+        <v>0.5810703003387968</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5707648234430358</v>
+        <v>0.5707065507996555</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5539879847310144</v>
+        <v>0.5539297944738489</v>
       </c>
       <c r="K17" t="n">
-        <v>0.545031199227467</v>
+        <v>0.5449760555973105</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5460195123879444</v>
+        <v>0.5459694231388142</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5543525714102941</v>
+        <v>0.5543085764772551</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5567893072302713</v>
+        <v>0.5567517182746576</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5449483301526564</v>
+        <v>0.5449168063719044</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5335396457047682</v>
+        <v>0.5335125162138507</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.5033386059765118</v>
+        <v>0.5033151873131457</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4659799635864642</v>
+        <v>0.4659591199763222</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4236378662828614</v>
+        <v>0.4236186760219189</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3784458281425031</v>
+        <v>0.3784270665784323</v>
       </c>
       <c r="U17" t="n">
-        <v>0.332592172358626</v>
+        <v>0.3325722874850452</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2884427931345164</v>
+        <v>0.2884208762917917</v>
       </c>
     </row>
     <row r="18">
@@ -1742,58 +1742,58 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.7533554638517134</v>
+        <v>0.7533549166685667</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8789266607173473</v>
+        <v>0.8789276278480902</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8510262433835265</v>
+        <v>0.8510238471182771</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8253785663987669</v>
+        <v>0.8253706581279776</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7920772701541741</v>
+        <v>0.7920659485198629</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7743089312441225</v>
+        <v>0.7742981695121789</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7640384457867909</v>
+        <v>0.7640300067098935</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7555015174304843</v>
+        <v>0.7554956939582308</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7382635486640738</v>
+        <v>0.7382591713386197</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7003030534239892</v>
+        <v>0.7002986812246617</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6416488027045453</v>
+        <v>0.6416429163826003</v>
       </c>
       <c r="P18" t="n">
-        <v>0.589170107838992</v>
+        <v>0.5891619594809314</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.526392809563498</v>
+        <v>0.526382403043579</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4701862179052753</v>
+        <v>0.4701746140247035</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4210685348299979</v>
+        <v>0.4210569288860035</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3772498825499493</v>
+        <v>0.3772392246506128</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3375101095798283</v>
+        <v>0.3375005788515831</v>
       </c>
       <c r="V18" t="n">
-        <v>0.298425022961546</v>
+        <v>0.2984163649405656</v>
       </c>
     </row>
     <row r="19">
@@ -1818,58 +1818,58 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.4082858763262973</v>
+        <v>0.4082890449741342</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5117539428557947</v>
+        <v>0.5117605734352951</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4870151954630705</v>
+        <v>0.4870229566555703</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4636276202839077</v>
+        <v>0.4636355931493656</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4400521605958802</v>
+        <v>0.4400597528879374</v>
       </c>
       <c r="J19" t="n">
-        <v>0.417706946822011</v>
+        <v>0.4177139309992271</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4162795449360205</v>
+        <v>0.4162862278699709</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4382486708090449</v>
+        <v>0.4382553380073444</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4668006855727705</v>
+        <v>0.4668074557297173</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4888964282366909</v>
+        <v>0.4889032380576731</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4767885830821845</v>
+        <v>0.476795018720557</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4511196216831482</v>
+        <v>0.45112559762331</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.4037022271204586</v>
+        <v>0.4037075845664737</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3462347854224606</v>
+        <v>0.3462394740264045</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2850878581348779</v>
+        <v>0.285091907536654</v>
       </c>
       <c r="T19" t="n">
-        <v>0.22955986824402</v>
+        <v>0.2295634125787507</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1841686434593801</v>
+        <v>0.1841718337405077</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1517050608921084</v>
+        <v>0.1517081425740133</v>
       </c>
     </row>
     <row r="20">
@@ -1894,58 +1894,58 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9002531616839745</v>
+        <v>0.9002621457556882</v>
       </c>
       <c r="F20" t="n">
-        <v>1.108495811752497</v>
+        <v>1.108514279048042</v>
       </c>
       <c r="G20" t="n">
-        <v>1.117938151477531</v>
+        <v>1.117961551044639</v>
       </c>
       <c r="H20" t="n">
-        <v>1.116696585091619</v>
+        <v>1.116722253501213</v>
       </c>
       <c r="I20" t="n">
-        <v>1.07513911155672</v>
+        <v>1.075164546285463</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9942612745170815</v>
+        <v>0.9942841459583155</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9342154249818282</v>
+        <v>0.9342359112550404</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9045492601794528</v>
+        <v>0.9045682971792217</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8782103979333262</v>
+        <v>0.8782277332154022</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8381846691848663</v>
+        <v>0.8382000271836578</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7497637410918535</v>
+        <v>0.7497764649498198</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6549136763934496</v>
+        <v>0.6549245881400226</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.545144488195528</v>
+        <v>0.5451532049539716</v>
       </c>
       <c r="R20" t="n">
-        <v>0.438098059222603</v>
+        <v>0.4381049480219826</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3404767480330644</v>
+        <v>0.3404821648667501</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2608080792421662</v>
+        <v>0.2608123855071789</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2006642465090613</v>
+        <v>0.2006678239778054</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1598204624133424</v>
+        <v>0.1598237287692698</v>
       </c>
     </row>
     <row r="21">
@@ -1970,58 +1970,58 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.07051006735231739</v>
+        <v>0.07050917997000647</v>
       </c>
       <c r="F21" t="n">
-        <v>0.07739649639374838</v>
+        <v>0.07739393452898409</v>
       </c>
       <c r="G21" t="n">
-        <v>0.06964990194207275</v>
+        <v>0.06964658987359905</v>
       </c>
       <c r="H21" t="n">
-        <v>0.06705444679503657</v>
+        <v>0.06705120335631039</v>
       </c>
       <c r="I21" t="n">
-        <v>0.06662693906699518</v>
+        <v>0.06662334441152894</v>
       </c>
       <c r="J21" t="n">
-        <v>0.06681173098572273</v>
+        <v>0.06680817096334996</v>
       </c>
       <c r="K21" t="n">
-        <v>0.06983857973148969</v>
+        <v>0.06983503748289389</v>
       </c>
       <c r="L21" t="n">
-        <v>0.07615177718951849</v>
+        <v>0.07614823661870766</v>
       </c>
       <c r="M21" t="n">
-        <v>0.08333162055335969</v>
+        <v>0.08332806324110673</v>
       </c>
       <c r="N21" t="n">
-        <v>0.08927396533992553</v>
+        <v>0.08926997297970604</v>
       </c>
       <c r="O21" t="n">
-        <v>0.09048448012765523</v>
+        <v>0.09048123685460893</v>
       </c>
       <c r="P21" t="n">
-        <v>0.08943635008959884</v>
+        <v>0.08943304233348962</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.08310298593768865</v>
+        <v>0.08310002054592863</v>
       </c>
       <c r="R21" t="n">
-        <v>0.07278161374513879</v>
+        <v>0.07277899814772108</v>
       </c>
       <c r="S21" t="n">
-        <v>0.06027708673286881</v>
+        <v>0.06027528465994433</v>
       </c>
       <c r="T21" t="n">
-        <v>0.04835783781004532</v>
+        <v>0.04835596813132623</v>
       </c>
       <c r="U21" t="n">
-        <v>0.03851991615480401</v>
+        <v>0.03851796898350843</v>
       </c>
       <c r="V21" t="n">
-        <v>0.03153173551238053</v>
+        <v>0.03153020909389255</v>
       </c>
     </row>
     <row r="22">
@@ -2046,58 +2046,58 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.06768796718187543</v>
+        <v>0.06768687470103091</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08885530458668635</v>
+        <v>0.08885311482636458</v>
       </c>
       <c r="G22" t="n">
-        <v>0.08795515492229654</v>
+        <v>0.08795249025146831</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0860732030494389</v>
+        <v>0.08607026271569225</v>
       </c>
       <c r="I22" t="n">
-        <v>0.08364130153103005</v>
+        <v>0.08363825102140243</v>
       </c>
       <c r="J22" t="n">
-        <v>0.08019472776350561</v>
+        <v>0.08019166876736618</v>
       </c>
       <c r="K22" t="n">
-        <v>0.08054840731173293</v>
+        <v>0.08054529039793693</v>
       </c>
       <c r="L22" t="n">
-        <v>0.08590688708794328</v>
+        <v>0.08590358975668089</v>
       </c>
       <c r="M22" t="n">
-        <v>0.09397740649449471</v>
+        <v>0.09397397259383068</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1021992008302849</v>
+        <v>0.1021957720155494</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1041208620236903</v>
+        <v>0.1041176238439319</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1030276850332309</v>
+        <v>0.1030247423587925</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.09624561509388414</v>
+        <v>0.09624305015955401</v>
       </c>
       <c r="R22" t="n">
-        <v>0.0857309706754224</v>
+        <v>0.08572877129418166</v>
       </c>
       <c r="S22" t="n">
-        <v>0.07281813955616143</v>
+        <v>0.07281629945060071</v>
       </c>
       <c r="T22" t="n">
-        <v>0.06007190094755845</v>
+        <v>0.06007034195043013</v>
       </c>
       <c r="U22" t="n">
-        <v>0.04907113336632829</v>
+        <v>0.04906975193473479</v>
       </c>
       <c r="V22" t="n">
-        <v>0.04095575403917132</v>
+        <v>0.04095444339562622</v>
       </c>
     </row>
     <row r="23">
@@ -2122,58 +2122,58 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.07703178082031444</v>
+        <v>0.07703072740945788</v>
       </c>
       <c r="F23" t="n">
-        <v>0.09990328849950642</v>
+        <v>0.09990118048700231</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1009323917690989</v>
+        <v>0.1009298320113251</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1033617597156181</v>
+        <v>0.1033591658922937</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1049312178564543</v>
+        <v>0.1049286396470319</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1057491238472824</v>
+        <v>0.1057466917548985</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1108785353763128</v>
+        <v>0.1108761533682864</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1220771405200489</v>
+        <v>0.122074728557429</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1354106251741824</v>
+        <v>0.1354082017672273</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1476558579211987</v>
+        <v>0.1476534642654086</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1499840865814073</v>
+        <v>0.1499819148069771</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1477705939692389</v>
+        <v>0.1477686664567263</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1373736089449225</v>
+        <v>0.1373719738809512</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1217278240861221</v>
+        <v>0.1217264594550142</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1028788384867484</v>
+        <v>0.1028777282611931</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0845568763618887</v>
+        <v>0.08455596248023732</v>
       </c>
       <c r="U23" t="n">
-        <v>0.06896634236780697</v>
+        <v>0.06896554786130533</v>
       </c>
       <c r="V23" t="n">
-        <v>0.05762125244160926</v>
+        <v>0.05762050288893995</v>
       </c>
     </row>
     <row r="24">
@@ -2198,58 +2198,58 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.4525835616058759</v>
+        <v>0.4525872291801994</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5530530490334992</v>
+        <v>0.5530603152385706</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5381427681534935</v>
+        <v>0.5381518328442026</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5265811545387848</v>
+        <v>0.5265908813001623</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5062509594301002</v>
+        <v>0.5062603442485475</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4782291085949364</v>
+        <v>0.4782379059020482</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4650379738916328</v>
+        <v>0.4650459536116532</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4679849438668353</v>
+        <v>0.4679921829976737</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4692991958005066</v>
+        <v>0.4693060634306809</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4577091913211062</v>
+        <v>0.4577151049006768</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4132139088326571</v>
+        <v>0.4132185878242035</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3612070361189746</v>
+        <v>0.3612108084998027</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.2992329713325187</v>
+        <v>0.2992358398017314</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2386902499862652</v>
+        <v>0.2386922004896414</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1849629737844654</v>
+        <v>0.1849643079423083</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1423496936821865</v>
+        <v>0.1423507259821646</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1108181942406335</v>
+        <v>0.1108189078018283</v>
       </c>
       <c r="V24" t="n">
-        <v>0.0896658336067063</v>
+        <v>0.08966657663625324</v>
       </c>
     </row>
     <row r="25">
@@ -2274,34 +2274,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.2186057303601927</v>
+        <v>0.2186065277053523</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2514789919148694</v>
+        <v>0.2514805066934278</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2399635248810341</v>
+        <v>0.2399649792318701</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2407697452525885</v>
+        <v>0.2407718617980477</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2393952410059859</v>
+        <v>0.2393973060635597</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2327633625911565</v>
+        <v>0.2327647124330563</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2316526709359796</v>
+        <v>0.2316546657348739</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2384617764969783</v>
+        <v>0.2384637516846705</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2447034016306701</v>
+        <v>0.2447040568867082</v>
       </c>
       <c r="N25" t="n">
-        <v>0.2444718862675608</v>
+        <v>0.2444725420732115</v>
       </c>
       <c r="O25" t="n">
         <v>0.2261061365582432</v>
@@ -2310,22 +2310,22 @@
         <v>0.2021994110391716</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1708750148812055</v>
+        <v>0.1708743345975272</v>
       </c>
       <c r="R25" t="n">
-        <v>0.13847732862524</v>
+        <v>0.1384766332589523</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1079968147457862</v>
+        <v>0.1079961012031755</v>
       </c>
       <c r="T25" t="n">
-        <v>0.08273406399013841</v>
+        <v>0.08273332936636496</v>
       </c>
       <c r="U25" t="n">
-        <v>0.06378959538624705</v>
+        <v>0.06378883674494328</v>
       </c>
       <c r="V25" t="n">
-        <v>0.05138591493959336</v>
+        <v>0.05138512916216482</v>
       </c>
     </row>
     <row r="26">
@@ -2350,58 +2350,58 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.07008593467968481</v>
+        <v>0.07008496647952742</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08741606167133933</v>
+        <v>0.08741401926820873</v>
       </c>
       <c r="G26" t="n">
-        <v>0.07985819502725784</v>
+        <v>0.0798555327351405</v>
       </c>
       <c r="H26" t="n">
-        <v>0.07205057118093548</v>
+        <v>0.07204740892326759</v>
       </c>
       <c r="I26" t="n">
-        <v>0.06527458982342969</v>
+        <v>0.06527114524822919</v>
       </c>
       <c r="J26" t="n">
-        <v>0.06014411393648594</v>
+        <v>0.06014058509043153</v>
       </c>
       <c r="K26" t="n">
-        <v>0.05916063157481551</v>
+        <v>0.05915697617365363</v>
       </c>
       <c r="L26" t="n">
-        <v>0.06225393730308192</v>
+        <v>0.0622500793641552</v>
       </c>
       <c r="M26" t="n">
-        <v>0.06654560837222896</v>
+        <v>0.06654153733837398</v>
       </c>
       <c r="N26" t="n">
-        <v>0.06991694862778432</v>
+        <v>0.06991272973057967</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0682645493395409</v>
+        <v>0.06826044980367778</v>
       </c>
       <c r="P26" t="n">
-        <v>0.06451423090124822</v>
+        <v>0.06451033159980005</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.05754444127268353</v>
+        <v>0.05754088626711932</v>
       </c>
       <c r="R26" t="n">
-        <v>0.04925567696778486</v>
+        <v>0.04925251756784337</v>
       </c>
       <c r="S26" t="n">
-        <v>0.04057492054166795</v>
+        <v>0.04057216107810346</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0327346579013155</v>
+        <v>0.03273225538169686</v>
       </c>
       <c r="U26" t="n">
-        <v>0.02631671096481168</v>
+        <v>0.02631454112886624</v>
       </c>
       <c r="V26" t="n">
-        <v>0.02169668729624234</v>
+        <v>0.02169457146087473</v>
       </c>
     </row>
     <row r="27">
@@ -2426,58 +2426,58 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.09708660433089587</v>
+        <v>0.09708606086297271</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1219120738093989</v>
+        <v>0.1219109148954599</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1147758894013296</v>
+        <v>0.114774340090358</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1095719066192078</v>
+        <v>0.109570130971756</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1047899694036092</v>
+        <v>0.1047880026934564</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1006591913488667</v>
+        <v>0.1006571829502677</v>
       </c>
       <c r="K27" t="n">
-        <v>0.1011341116242322</v>
+        <v>0.1011320108072616</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1064733522986623</v>
+        <v>0.106471073945142</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1122004433792871</v>
+        <v>0.1121979516360182</v>
       </c>
       <c r="N27" t="n">
-        <v>0.1150762344087561</v>
+        <v>0.1150735686146197</v>
       </c>
       <c r="O27" t="n">
-        <v>0.1089806600879435</v>
+        <v>0.1089779260546977</v>
       </c>
       <c r="P27" t="n">
-        <v>0.09966191746994686</v>
+        <v>0.0996592439201046</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.08608191087826038</v>
+        <v>0.08607935020306154</v>
       </c>
       <c r="R27" t="n">
-        <v>0.07123156439483028</v>
+        <v>0.07122920231578229</v>
       </c>
       <c r="S27" t="n">
-        <v>0.05664358602536748</v>
+        <v>0.05664147519540254</v>
       </c>
       <c r="T27" t="n">
-        <v>0.04417662495304377</v>
+        <v>0.04417471996706046</v>
       </c>
       <c r="U27" t="n">
-        <v>0.03447004191569637</v>
+        <v>0.03446826682028499</v>
       </c>
       <c r="V27" t="n">
-        <v>0.02774672765335247</v>
+        <v>0.02774494040714143</v>
       </c>
     </row>
     <row r="28">
@@ -2502,58 +2502,58 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.2685680992345001</v>
+        <v>0.2685687295349328</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3356494623105959</v>
+        <v>0.3356507797019441</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3935069768872586</v>
+        <v>0.3935102836511287</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4963137785505512</v>
+        <v>0.4963204126074852</v>
       </c>
       <c r="I28" t="n">
-        <v>0.620944796022501</v>
+        <v>0.620955296694544</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7463153360115233</v>
+        <v>0.7463294331304346</v>
       </c>
       <c r="K28" t="n">
-        <v>0.8995939291121282</v>
+        <v>0.899611782780897</v>
       </c>
       <c r="L28" t="n">
-        <v>1.099128358608837</v>
+        <v>1.099150331388729</v>
       </c>
       <c r="M28" t="n">
-        <v>1.317636029258098</v>
+        <v>1.317662277951933</v>
       </c>
       <c r="N28" t="n">
-        <v>1.517805100807559</v>
+        <v>1.51783497225732</v>
       </c>
       <c r="O28" t="n">
-        <v>1.597868162396175</v>
+        <v>1.597899450735408</v>
       </c>
       <c r="P28" t="n">
-        <v>1.610532507296947</v>
+        <v>1.610564022498956</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.521366847398037</v>
+        <v>1.521397233383945</v>
       </c>
       <c r="R28" t="n">
-        <v>1.365243018147674</v>
+        <v>1.365271177172161</v>
       </c>
       <c r="S28" t="n">
-        <v>1.166740837488487</v>
+        <v>1.16676634404675</v>
       </c>
       <c r="T28" t="n">
-        <v>0.969280791703547</v>
+        <v>0.9693038793629776</v>
       </c>
       <c r="U28" t="n">
-        <v>0.7994899193287212</v>
+        <v>0.7995113682432469</v>
       </c>
       <c r="V28" t="n">
-        <v>0.6762476624096112</v>
+        <v>0.6762691056708519</v>
       </c>
     </row>
     <row r="29">
@@ -2578,19 +2578,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.1390042981369429</v>
+        <v>0.1390047960675433</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1584120381480593</v>
+        <v>0.1584128380840644</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1608810995922072</v>
+        <v>0.1608819846989189</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1698567744911628</v>
+        <v>0.1698578833910454</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1798590512081031</v>
+        <v>0.1798609025495028</v>
       </c>
       <c r="J29" t="n">
         <v>0.1846501626119684</v>
@@ -2654,19 +2654,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.05031100425878256</v>
+        <v>0.05030993192274677</v>
       </c>
       <c r="F30" t="n">
-        <v>0.05429188694810601</v>
+        <v>0.0542888191061363</v>
       </c>
       <c r="G30" t="n">
-        <v>0.05193236924367912</v>
+        <v>0.05192682119147889</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0530595080389223</v>
+        <v>0.05304934224111366</v>
       </c>
       <c r="I30" t="n">
-        <v>0.05439161490455482</v>
+        <v>0.05436880779695074</v>
       </c>
       <c r="J30" t="n">
         <v>0.18182471532223</v>
@@ -2730,19 +2730,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.01167121437425152</v>
+        <v>0.0116695365113455</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01459877175264684</v>
+        <v>0.01459409983422476</v>
       </c>
       <c r="G31" t="n">
-        <v>0.01539781216872353</v>
+        <v>0.01539016470096398</v>
       </c>
       <c r="H31" t="n">
-        <v>0.01682956473255438</v>
+        <v>0.01681578074079996</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0184110181782981</v>
+        <v>0.01838077771567161</v>
       </c>
       <c r="J31" t="n">
         <v>0.183287532788577</v>
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.1275890186526046</v>
+        <v>0.1275893485869853</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1406001758952446</v>
+        <v>0.1406002647312267</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1379456329302547</v>
+        <v>0.137945126373297</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1457322799128198</v>
+        <v>0.1457309818642331</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1584549229270007</v>
+        <v>0.1584523336885036</v>
       </c>
       <c r="J32" t="n">
         <v>0.1855301319084504</v>
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.1029557066427433</v>
+        <v>0.1029555199360716</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1207583463717268</v>
+        <v>0.1207576120171511</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1257223588395064</v>
+        <v>0.1257209850344138</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1363395567991705</v>
+        <v>0.1363370734746943</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1470708966356334</v>
+        <v>0.1470654390180363</v>
       </c>
       <c r="J33" t="n">
         <v>0.1883991414689768</v>
@@ -2958,19 +2958,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.01122557732167258</v>
+        <v>0.0112238384815485</v>
       </c>
       <c r="F34" t="n">
-        <v>0.02227105090862446</v>
+        <v>0.02226684265816465</v>
       </c>
       <c r="G34" t="n">
-        <v>0.03792746946669686</v>
+        <v>0.03792092730661095</v>
       </c>
       <c r="H34" t="n">
-        <v>0.05757248752995221</v>
+        <v>0.05756234040649455</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0757541599570585</v>
+        <v>0.07573439959241973</v>
       </c>
       <c r="J34" t="n">
         <v>0.1891792847197873</v>
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.3059987805637002</v>
+        <v>0.3060021026749418</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4329462115472163</v>
+        <v>0.4329570699393056</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5294315410536443</v>
+        <v>0.5294542621213202</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6193375808168647</v>
+        <v>0.6193820663765773</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6703542114008005</v>
+        <v>0.6704527721084793</v>
       </c>
       <c r="J35" t="n">
         <v>0.1928622057142177</v>
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.3681049439642371</v>
+        <v>0.368110805445707</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4520579390767394</v>
+        <v>0.4520694167068384</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4354942354942355</v>
+        <v>0.4355112455112455</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4225131107025528</v>
+        <v>0.4225375990837578</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4087612739757839</v>
+        <v>0.4088065870038459</v>
       </c>
       <c r="J36" t="n">
         <v>0.1919956733369389</v>
@@ -3186,19 +3186,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9540170078134345</v>
+        <v>0.954032420142558</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9979367326090687</v>
+        <v>0.9979678284614578</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9152368955695807</v>
+        <v>0.9152831063658363</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8876091404635235</v>
+        <v>0.8876797504559796</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8687651292999194</v>
+        <v>0.8689030545444368</v>
       </c>
       <c r="J37" t="n">
         <v>0.1954140974436443</v>
@@ -3262,19 +3262,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.1408668612249747</v>
+        <v>0.1408674181666964</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1670505181329472</v>
+        <v>0.1670515417065292</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1700362359872237</v>
+        <v>0.1700376317531677</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1832881483121703</v>
+        <v>0.1832904430774531</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1999842232411379</v>
+        <v>0.199989716933956</v>
       </c>
       <c r="J38" t="n">
         <v>0.1866675095828021</v>
@@ -3338,19 +3338,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.06355704697986576</v>
+        <v>0.06355621037758651</v>
       </c>
       <c r="F39" t="n">
-        <v>0.07321150611113826</v>
+        <v>0.07320915030398638</v>
       </c>
       <c r="G39" t="n">
-        <v>0.07662452034975152</v>
+        <v>0.07662038186615813</v>
       </c>
       <c r="H39" t="n">
-        <v>0.08547344176930889</v>
+        <v>0.08546628900047208</v>
       </c>
       <c r="I39" t="n">
-        <v>0.09695123780945236</v>
+        <v>0.09693661877007713</v>
       </c>
       <c r="J39" t="n">
         <v>0.1843217121004089</v>
@@ -3414,19 +3414,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.05254896807493228</v>
+        <v>0.05254775132564835</v>
       </c>
       <c r="F40" t="n">
-        <v>0.06320058386947253</v>
+        <v>0.06319775065192336</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0661407754053449</v>
+        <v>0.06613597842424501</v>
       </c>
       <c r="H40" t="n">
-        <v>0.07107792543061277</v>
+        <v>0.07106930328498676</v>
       </c>
       <c r="I40" t="n">
-        <v>0.07679192737355564</v>
+        <v>0.07677298894529949</v>
       </c>
       <c r="J40" t="n">
         <v>0.1848166599576088</v>
@@ -3490,19 +3490,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.0626488472945009</v>
+        <v>0.06264781340836589</v>
       </c>
       <c r="F41" t="n">
-        <v>0.08111315442453812</v>
+        <v>0.08111079796364075</v>
       </c>
       <c r="G41" t="n">
-        <v>0.08573704108852936</v>
+        <v>0.08573311559954429</v>
       </c>
       <c r="H41" t="n">
-        <v>0.09207529961549499</v>
+        <v>0.09206834061912963</v>
       </c>
       <c r="I41" t="n">
-        <v>0.09607573351146662</v>
+        <v>0.09606023467562293</v>
       </c>
       <c r="J41" t="n">
         <v>0.1887037731125178</v>
@@ -3566,19 +3566,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1.64619706317258</v>
+        <v>1.646224938831934</v>
       </c>
       <c r="F42" t="n">
-        <v>1.728525186074867</v>
+        <v>1.728583192298593</v>
       </c>
       <c r="G42" t="n">
-        <v>1.512713936683117</v>
+        <v>1.512795618543643</v>
       </c>
       <c r="H42" t="n">
-        <v>1.380545931918675</v>
+        <v>1.380665101885555</v>
       </c>
       <c r="I42" t="n">
-        <v>1.291451593714987</v>
+        <v>1.29167265941145</v>
       </c>
       <c r="J42" t="n">
         <v>0.1997398778462354</v>
@@ -3642,19 +3642,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.06134875487687743</v>
+        <v>0.06134792019710128</v>
       </c>
       <c r="F43" t="n">
-        <v>0.09214967636844386</v>
+        <v>0.09214806322931812</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1135217821226424</v>
+        <v>0.1135198953601523</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1357344791026784</v>
+        <v>0.1357323676649357</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1557155583332258</v>
+        <v>0.155712747730662</v>
       </c>
       <c r="J43" t="n">
         <v>0.1838971590693453</v>
@@ -3718,19 +3718,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.04814820108675766</v>
+        <v>0.04814711478649054</v>
       </c>
       <c r="F44" t="n">
-        <v>0.06141502225706464</v>
+        <v>0.06141211683467993</v>
       </c>
       <c r="G44" t="n">
-        <v>0.06522686441122331</v>
+        <v>0.0652218968795622</v>
       </c>
       <c r="H44" t="n">
-        <v>0.07266289506705605</v>
+        <v>0.07265430218878301</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0817058161368371</v>
+        <v>0.08168759983932292</v>
       </c>
       <c r="J44" t="n">
         <v>0.1870088644008385</v>
@@ -3794,19 +3794,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.1715199340638991</v>
+        <v>0.1715212381798193</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2064317044519724</v>
+        <v>0.206434099337455</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2125639950561941</v>
+        <v>0.2125677924852453</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2259108481631791</v>
+        <v>0.2259171764640366</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2365637037406051</v>
+        <v>0.2365763588358276</v>
       </c>
       <c r="J45" t="n">
         <v>0.1876781430877343</v>
@@ -3870,19 +3870,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.02879019341645351</v>
+        <v>0.02878875796194168</v>
       </c>
       <c r="F46" t="n">
-        <v>0.03673034568266616</v>
+        <v>0.03672665817102296</v>
       </c>
       <c r="G46" t="n">
-        <v>0.04039227128614715</v>
+        <v>0.04038600685219761</v>
       </c>
       <c r="H46" t="n">
-        <v>0.04466832100184365</v>
+        <v>0.04465732865872102</v>
       </c>
       <c r="I46" t="n">
-        <v>0.04867793915295279</v>
+        <v>0.04865386180270705</v>
       </c>
       <c r="J46" t="n">
         <v>0.1826277761856457</v>
@@ -3946,19 +3946,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.159296761433228</v>
+        <v>0.1592976012724974</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2096357031623948</v>
+        <v>0.2096381747704917</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2216868695531583</v>
+        <v>0.2216911348773047</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2375384106114298</v>
+        <v>0.2375456167544695</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2517958285786352</v>
+        <v>0.2518108334181708</v>
       </c>
       <c r="J47" t="n">
         <v>0.1911488833729543</v>
@@ -4022,19 +4022,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.1602213050007378</v>
+        <v>0.1602222453697676</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1954199178876894</v>
+        <v>0.1954219793402553</v>
       </c>
       <c r="G48" t="n">
-        <v>0.2051480384349159</v>
+        <v>0.205151449744586</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2173601846049325</v>
+        <v>0.2173656899550787</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2270385289796693</v>
+        <v>0.2270492337971158</v>
       </c>
       <c r="J48" t="n">
         <v>0.1873672176541938</v>
@@ -4098,19 +4098,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.03740042779114391</v>
+        <v>0.03739904702787638</v>
       </c>
       <c r="F49" t="n">
-        <v>0.04749507650007098</v>
+        <v>0.04749172646822473</v>
       </c>
       <c r="G49" t="n">
-        <v>0.05033325869954387</v>
+        <v>0.05032748142799773</v>
       </c>
       <c r="H49" t="n">
-        <v>0.05381669330863349</v>
+        <v>0.0538062954718616</v>
       </c>
       <c r="I49" t="n">
-        <v>0.05684707381962305</v>
+        <v>0.05682408763633751</v>
       </c>
       <c r="J49" t="n">
         <v>0.185380010305357</v>
@@ -4177,16 +4177,16 @@
         <v>0.1923465347670909</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2289457681463873</v>
+        <v>0.2289512963679584</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2203718778808675</v>
+        <v>0.2203772689780097</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2149638588820986</v>
+        <v>0.2149691776632467</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2103780727343961</v>
+        <v>0.2103833671292203</v>
       </c>
       <c r="J50" t="n">
         <v>0.1868912661663739</v>
@@ -4250,19 +4250,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.03037121185227259</v>
+        <v>0.03036979185156259</v>
       </c>
       <c r="F51" t="n">
-        <v>0.03375210082553195</v>
+        <v>0.03374822508870153</v>
       </c>
       <c r="G51" t="n">
-        <v>0.03252781201153307</v>
+        <v>0.03252094406310373</v>
       </c>
       <c r="H51" t="n">
-        <v>0.03253519346577225</v>
+        <v>0.03252272890095739</v>
       </c>
       <c r="I51" t="n">
-        <v>0.03311667252090826</v>
+        <v>0.03308898159900529</v>
       </c>
       <c r="J51" t="n">
         <v>0.1851997498714057</v>
@@ -4326,19 +4326,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.0562957337439112</v>
+        <v>0.05629482386485384</v>
       </c>
       <c r="F52" t="n">
-        <v>0.05947561154240515</v>
+        <v>0.05947282150006626</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0539547107510495</v>
+        <v>0.05394939173115546</v>
       </c>
       <c r="H52" t="n">
-        <v>0.05199687850851647</v>
+        <v>0.05198685963026185</v>
       </c>
       <c r="I52" t="n">
-        <v>0.05231979176156096</v>
+        <v>0.05229693009610604</v>
       </c>
       <c r="J52" t="n">
         <v>0.1800332311358597</v>
@@ -4478,58 +4478,58 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3.056248238646121</v>
+        <v>3.056427012185154</v>
       </c>
       <c r="F54" t="n">
-        <v>3.148732181075521</v>
+        <v>3.14888649720434</v>
       </c>
       <c r="G54" t="n">
-        <v>2.837663409841679</v>
+        <v>2.837810437957538</v>
       </c>
       <c r="H54" t="n">
-        <v>2.387287164462723</v>
+        <v>2.387420161440095</v>
       </c>
       <c r="I54" t="n">
-        <v>1.932337007285635</v>
+        <v>1.932450110625233</v>
       </c>
       <c r="J54" t="n">
-        <v>1.557139334630541</v>
+        <v>1.557231612410443</v>
       </c>
       <c r="K54" t="n">
-        <v>1.24303351232568</v>
+        <v>1.243105826875075</v>
       </c>
       <c r="L54" t="n">
-        <v>1.015579064965331</v>
+        <v>1.015635579371039</v>
       </c>
       <c r="M54" t="n">
-        <v>0.8608456968939829</v>
+        <v>0.8608909466875161</v>
       </c>
       <c r="N54" t="n">
-        <v>0.7328630547529202</v>
+        <v>0.7328992332628349</v>
       </c>
       <c r="O54" t="n">
-        <v>0.5755713601940408</v>
+        <v>0.5755982042615753</v>
       </c>
       <c r="P54" t="n">
-        <v>0.3002386091674594</v>
+        <v>0.3002518054664713</v>
       </c>
       <c r="Q54" t="n">
-        <v>-0.09103388549881142</v>
+        <v>-0.09103759872058359</v>
       </c>
       <c r="R54" t="n">
-        <v>-0.5242074995738243</v>
+        <v>-0.5242272014651127</v>
       </c>
       <c r="S54" t="n">
-        <v>-0.9504587367294891</v>
+        <v>-0.9504912186079282</v>
       </c>
       <c r="T54" t="n">
-        <v>-1.30552750414643</v>
+        <v>-1.305567270531797</v>
       </c>
       <c r="U54" t="n">
-        <v>-1.571826895280448</v>
+        <v>-1.571868443600408</v>
       </c>
       <c r="V54" t="n">
-        <v>-1.794423869146899</v>
+        <v>-1.794463756910983</v>
       </c>
     </row>
     <row r="55">
@@ -4554,58 +4554,58 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>10.46868728941161</v>
+        <v>10.46775110023899</v>
       </c>
       <c r="F55" t="n">
-        <v>12.39565551020812</v>
+        <v>12.39482847058184</v>
       </c>
       <c r="G55" t="n">
-        <v>12.21819306191832</v>
+        <v>12.21738711202861</v>
       </c>
       <c r="H55" t="n">
-        <v>10.77411143030256</v>
+        <v>10.77336668515498</v>
       </c>
       <c r="I55" t="n">
-        <v>8.859668530950167</v>
+        <v>8.859022559802698</v>
       </c>
       <c r="J55" t="n">
-        <v>7.078406419737232</v>
+        <v>7.077868541136748</v>
       </c>
       <c r="K55" t="n">
-        <v>5.505527944183071</v>
+        <v>5.505098295352105</v>
       </c>
       <c r="L55" t="n">
-        <v>4.332335593883311</v>
+        <v>4.33199325177351</v>
       </c>
       <c r="M55" t="n">
-        <v>3.514499773403187</v>
+        <v>3.514220847746646</v>
       </c>
       <c r="N55" t="n">
-        <v>2.852777670183039</v>
+        <v>2.852550957088144</v>
       </c>
       <c r="O55" t="n">
-        <v>2.139614781364431</v>
+        <v>2.139444476269918</v>
       </c>
       <c r="P55" t="n">
-        <v>1.06517341544395</v>
+        <v>1.0650889881759</v>
       </c>
       <c r="Q55" t="n">
-        <v>-0.3066845151605525</v>
+        <v>-0.3066606082257106</v>
       </c>
       <c r="R55" t="n">
-        <v>-1.676282959159922</v>
+        <v>-1.676155831213157</v>
       </c>
       <c r="S55" t="n">
-        <v>-2.874794135736475</v>
+        <v>-2.8745843674096</v>
       </c>
       <c r="T55" t="n">
-        <v>-3.72639713354624</v>
+        <v>-3.726140962959877</v>
       </c>
       <c r="U55" t="n">
-        <v>-4.242711984154172</v>
+        <v>-4.242444755126999</v>
       </c>
       <c r="V55" t="n">
-        <v>-4.599838076623825</v>
+        <v>-4.599582489563399</v>
       </c>
     </row>
     <row r="56">
@@ -4782,19 +4782,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1.054297001631877</v>
+        <v>1.06153330512805</v>
       </c>
       <c r="F58" t="n">
-        <v>1.018008115009635</v>
+        <v>1.031146702037108</v>
       </c>
       <c r="G58" t="n">
-        <v>0.9799339395138369</v>
+        <v>0.9989106781091375</v>
       </c>
       <c r="H58" t="n">
-        <v>0.9161197037438906</v>
+        <v>0.941925858469408</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7738423341295305</v>
+        <v>0.8110327477280115</v>
       </c>
       <c r="J58" t="n">
         <v>0.1594835437200991</v>
@@ -4858,19 +4858,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.2608597412867875</v>
+        <v>0.2598013420264778</v>
       </c>
       <c r="F59" t="n">
-        <v>0.2800151719487525</v>
+        <v>0.2780849629130142</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2984163678001988</v>
+        <v>0.2960155338547293</v>
       </c>
       <c r="H59" t="n">
-        <v>0.3039300551739018</v>
+        <v>0.3005306903183879</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2968804929999793</v>
+        <v>0.2910669603159832</v>
       </c>
       <c r="J59" t="n">
         <v>0.3720352406224171</v>
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.8973935635570618</v>
+        <v>0.9029925214179187</v>
       </c>
       <c r="F60" t="n">
-        <v>0.7421229590401085</v>
+        <v>0.7497312390421288</v>
       </c>
       <c r="G60" t="n">
-        <v>0.6261357659079283</v>
+        <v>0.6339213016003401</v>
       </c>
       <c r="H60" t="n">
-        <v>0.5546403015635287</v>
+        <v>0.5626207375572486</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4852478887740833</v>
+        <v>0.49499257009124</v>
       </c>
       <c r="J60" t="n">
         <v>0.3093556650392398</v>
@@ -5010,19 +5010,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.5419826033930403</v>
+        <v>0.5438661061812881</v>
       </c>
       <c r="F61" t="n">
-        <v>0.5455566282288201</v>
+        <v>0.5488971727451943</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5276316057694828</v>
+        <v>0.5318205015827346</v>
       </c>
       <c r="H61" t="n">
-        <v>0.4969930010672176</v>
+        <v>0.5014943325890473</v>
       </c>
       <c r="I61" t="n">
-        <v>0.4443421450698526</v>
+        <v>0.4489612709427767</v>
       </c>
       <c r="J61" t="n">
         <v>0.355624041639273</v>
@@ -5086,19 +5086,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.9078014666732289</v>
+        <v>0.9128247553680329</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9911243381327115</v>
+        <v>1.002095493818039</v>
       </c>
       <c r="G62" t="n">
-        <v>1.006425202899929</v>
+        <v>1.023487819540263</v>
       </c>
       <c r="H62" t="n">
-        <v>0.9630295278274307</v>
+        <v>0.9867237442057746</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8278379312162186</v>
+        <v>0.8618490887193271</v>
       </c>
       <c r="J62" t="n">
         <v>0.261333402979859</v>
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.7886927330249365</v>
+        <v>0.7923854564802569</v>
       </c>
       <c r="F63" t="n">
-        <v>0.8138203629341572</v>
+        <v>0.821087497944451</v>
       </c>
       <c r="G63" t="n">
-        <v>0.7911255280305484</v>
+        <v>0.8012780385555718</v>
       </c>
       <c r="H63" t="n">
-        <v>0.7522131166073314</v>
+        <v>0.7655552966098009</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6677094816194343</v>
+        <v>0.6867126894030167</v>
       </c>
       <c r="J63" t="n">
         <v>0.3361282369539821</v>
@@ -5238,19 +5238,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.3888407851794057</v>
+        <v>0.389430716385815</v>
       </c>
       <c r="F64" t="n">
-        <v>0.3657865157836581</v>
+        <v>0.3658150921110285</v>
       </c>
       <c r="G64" t="n">
-        <v>0.3556144851507028</v>
+        <v>0.3547881897404856</v>
       </c>
       <c r="H64" t="n">
-        <v>0.3485758215665476</v>
+        <v>0.3466100952696061</v>
       </c>
       <c r="I64" t="n">
-        <v>0.334845914059109</v>
+        <v>0.3311762616896184</v>
       </c>
       <c r="J64" t="n">
         <v>0.3692867452489776</v>
@@ -5314,19 +5314,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.3822022055974562</v>
+        <v>0.3812703972031775</v>
       </c>
       <c r="F65" t="n">
-        <v>0.41920532468948</v>
+        <v>0.4179511603330537</v>
       </c>
       <c r="G65" t="n">
-        <v>0.4423226469570139</v>
+        <v>0.4410433910236229</v>
       </c>
       <c r="H65" t="n">
-        <v>0.4491737741722389</v>
+        <v>0.4476131758227146</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4332050116966347</v>
+        <v>0.4307690447250905</v>
       </c>
       <c r="J65" t="n">
         <v>0.4386605835671222</v>
@@ -5390,19 +5390,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.4615365742731028</v>
+        <v>0.4587821245661614</v>
       </c>
       <c r="F66" t="n">
-        <v>0.5126875017175883</v>
+        <v>0.5081690513979473</v>
       </c>
       <c r="G66" t="n">
-        <v>0.5518986772742025</v>
+        <v>0.5463007753909848</v>
       </c>
       <c r="H66" t="n">
-        <v>0.5753302531873251</v>
+        <v>0.5684746319384839</v>
       </c>
       <c r="I66" t="n">
-        <v>0.5749379216043099</v>
+        <v>0.5657311214994689</v>
       </c>
       <c r="J66" t="n">
         <v>0.6581634144595777</v>
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.1685059329019534</v>
+        <v>0.1545481456944817</v>
       </c>
       <c r="F67" t="n">
-        <v>0.2272258909776634</v>
+        <v>0.2021051996842474</v>
       </c>
       <c r="G67" t="n">
-        <v>0.2815613806577662</v>
+        <v>0.2481547222969434</v>
       </c>
       <c r="H67" t="n">
-        <v>0.3389273755967266</v>
+        <v>0.2971997207851577</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4261022852701524</v>
+        <v>0.3700288953932341</v>
       </c>
       <c r="J67" t="n">
         <v>1.134733962114981</v>
@@ -5542,19 +5542,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.8808851334423197</v>
+        <v>0.8848526249574177</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9769216495967997</v>
+        <v>0.9861469718418836</v>
       </c>
       <c r="G68" t="n">
-        <v>1.098893541753931</v>
+        <v>1.116529323996975</v>
       </c>
       <c r="H68" t="n">
-        <v>1.160803650146208</v>
+        <v>1.189999960106899</v>
       </c>
       <c r="I68" t="n">
-        <v>1.061465139133572</v>
+        <v>1.108657834625664</v>
       </c>
       <c r="J68" t="n">
         <v>0.2703025524177043</v>
@@ -5618,19 +5618,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.3497897772299023</v>
+        <v>0.3504006339702386</v>
       </c>
       <c r="F69" t="n">
-        <v>0.3506472750519419</v>
+        <v>0.351494326354483</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3447332279007824</v>
+        <v>0.3454979607125021</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3319390330689795</v>
+        <v>0.3321489460830744</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3074106152466913</v>
+        <v>0.3062963131796609</v>
       </c>
       <c r="J69" t="n">
         <v>0.306296229115021</v>
@@ -5694,19 +5694,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.3474849815674423</v>
+        <v>0.3396778916544655</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3980969471693762</v>
+        <v>0.3834937121752491</v>
       </c>
       <c r="G70" t="n">
-        <v>0.447672745639927</v>
+        <v>0.4273612543692079</v>
       </c>
       <c r="H70" t="n">
-        <v>0.4965095793791978</v>
+        <v>0.4700823210199462</v>
       </c>
       <c r="I70" t="n">
-        <v>0.5527015616393817</v>
+        <v>0.5163626306578175</v>
       </c>
       <c r="J70" t="n">
         <v>1.004861574068251</v>
@@ -5770,19 +5770,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.974935221857644</v>
+        <v>0.9802983857753195</v>
       </c>
       <c r="F71" t="n">
-        <v>1.052657877153816</v>
+        <v>1.06415523795423</v>
       </c>
       <c r="G71" t="n">
-        <v>1.024519695756123</v>
+        <v>1.041090749227647</v>
       </c>
       <c r="H71" t="n">
-        <v>0.9386390182577176</v>
+        <v>0.9596257836408473</v>
       </c>
       <c r="I71" t="n">
-        <v>0.7952211702818793</v>
+        <v>0.8234780379545522</v>
       </c>
       <c r="J71" t="n">
         <v>0.3211435594659512</v>
@@ -5846,19 +5846,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.4102852322505234</v>
+        <v>0.4093568361178307</v>
       </c>
       <c r="F72" t="n">
-        <v>0.4179937479689966</v>
+        <v>0.4156651026250228</v>
       </c>
       <c r="G72" t="n">
-        <v>0.4264337855777035</v>
+        <v>0.4226107638246006</v>
       </c>
       <c r="H72" t="n">
-        <v>0.4336242312035411</v>
+        <v>0.4280748836903929</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4309151673081588</v>
+        <v>0.4226902772328974</v>
       </c>
       <c r="J72" t="n">
         <v>0.5090961056342334</v>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>9.242481257075845</v>
+        <v>9.314597170030497</v>
       </c>
       <c r="F73" t="n">
-        <v>7.214767651530329</v>
+        <v>7.321890726096333</v>
       </c>
       <c r="G73" t="n">
-        <v>5.197310661692402</v>
+        <v>5.312626116073913</v>
       </c>
       <c r="H73" t="n">
-        <v>3.946643324878966</v>
+        <v>4.073012890964273</v>
       </c>
       <c r="I73" t="n">
-        <v>2.959664948750587</v>
+        <v>3.122007634215235</v>
       </c>
       <c r="J73" t="n">
         <v>0.3057267625565955</v>
@@ -5998,19 +5998,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.307310858127555</v>
+        <v>0.30684338851308</v>
       </c>
       <c r="F74" t="n">
-        <v>0.3664569921233698</v>
+        <v>0.3668997067015919</v>
       </c>
       <c r="G74" t="n">
-        <v>0.3864225625338084</v>
+        <v>0.3876816325007927</v>
       </c>
       <c r="H74" t="n">
-        <v>0.3789692128379339</v>
+        <v>0.3803432166851446</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3490105942229133</v>
+        <v>0.3497831902421123</v>
       </c>
       <c r="J74" t="n">
         <v>0.32196389577796</v>
@@ -6074,19 +6074,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.6076780237407345</v>
+        <v>0.5987391624371022</v>
       </c>
       <c r="F75" t="n">
-        <v>0.6605838266418778</v>
+        <v>0.6491612179739052</v>
       </c>
       <c r="G75" t="n">
-        <v>0.6817219633580589</v>
+        <v>0.6698325916133446</v>
       </c>
       <c r="H75" t="n">
-        <v>0.6158011878764508</v>
+        <v>0.602177354341226</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5627850318522926</v>
+        <v>0.5404752879701393</v>
       </c>
       <c r="J75" t="n">
         <v>1.350568296986968</v>
@@ -6150,19 +6150,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1.123340648442635</v>
+        <v>1.130221431752596</v>
       </c>
       <c r="F76" t="n">
-        <v>1.169458720328693</v>
+        <v>1.174680950200195</v>
       </c>
       <c r="G76" t="n">
-        <v>0.9432990244478886</v>
+        <v>0.9419613392673154</v>
       </c>
       <c r="H76" t="n">
-        <v>0.7001138158998883</v>
+        <v>0.6931293778128442</v>
       </c>
       <c r="I76" t="n">
-        <v>0.5701678337861241</v>
+        <v>0.5539544837755573</v>
       </c>
       <c r="J76" t="n">
         <v>1.166721359898617</v>
@@ -6226,19 +6226,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8159381891801396</v>
+        <v>0.8100444701468885</v>
       </c>
       <c r="F77" t="n">
-        <v>1.007264163621774</v>
+        <v>1.00301454147417</v>
       </c>
       <c r="G77" t="n">
-        <v>1.099865886566777</v>
+        <v>1.09650671985284</v>
       </c>
       <c r="H77" t="n">
-        <v>0.9683093520522182</v>
+        <v>0.9633102386166319</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8093676977860743</v>
+        <v>0.7976135050544049</v>
       </c>
       <c r="J77" t="n">
         <v>1.251795813997319</v>
@@ -6302,19 +6302,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3.804159862202144</v>
+        <v>3.845264390697453</v>
       </c>
       <c r="F78" t="n">
-        <v>3.373942356602782</v>
+        <v>3.404089583207603</v>
       </c>
       <c r="G78" t="n">
-        <v>2.792208790260876</v>
+        <v>2.808918979170937</v>
       </c>
       <c r="H78" t="n">
-        <v>2.136353277670621</v>
+        <v>2.14545901920892</v>
       </c>
       <c r="I78" t="n">
-        <v>1.707711708974095</v>
+        <v>1.714394365280054</v>
       </c>
       <c r="J78" t="n">
         <v>1.364378580275688</v>
@@ -6378,19 +6378,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.6614534008072236</v>
+        <v>0.6344039998872523</v>
       </c>
       <c r="F79" t="n">
-        <v>0.8630540467534493</v>
+        <v>0.8403728176130929</v>
       </c>
       <c r="G79" t="n">
-        <v>1.092469709064863</v>
+        <v>1.078325509997649</v>
       </c>
       <c r="H79" t="n">
-        <v>1.153766382876661</v>
+        <v>1.144364168644807</v>
       </c>
       <c r="I79" t="n">
-        <v>1.121702394876178</v>
+        <v>1.112243467720265</v>
       </c>
       <c r="J79" t="n">
         <v>1.316028375918729</v>
@@ -6454,19 +6454,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1.979247569309312</v>
+        <v>1.970601601256261</v>
       </c>
       <c r="F80" t="n">
-        <v>1.785533606593389</v>
+        <v>1.758880413404905</v>
       </c>
       <c r="G80" t="n">
-        <v>1.59728894326342</v>
+        <v>1.558075989653874</v>
       </c>
       <c r="H80" t="n">
-        <v>1.38816810584555</v>
+        <v>1.33939327448623</v>
       </c>
       <c r="I80" t="n">
-        <v>1.324430797162414</v>
+        <v>1.248469620858785</v>
       </c>
       <c r="J80" t="n">
         <v>3.791791412672875</v>
@@ -6530,19 +6530,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.3172820189102168</v>
+        <v>0.2821625472828562</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3954487470818592</v>
+        <v>0.3642882370141469</v>
       </c>
       <c r="G81" t="n">
-        <v>0.472177586569538</v>
+        <v>0.448737045837118</v>
       </c>
       <c r="H81" t="n">
-        <v>0.492698747865981</v>
+        <v>0.4722543169289154</v>
       </c>
       <c r="I81" t="n">
-        <v>0.5041072088734395</v>
+        <v>0.476801939698127</v>
       </c>
       <c r="J81" t="n">
         <v>1.382640860471509</v>
@@ -6606,19 +6606,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3.858105042980538</v>
+        <v>3.894425036788546</v>
       </c>
       <c r="F82" t="n">
-        <v>3.974512904908792</v>
+        <v>4.007169373617227</v>
       </c>
       <c r="G82" t="n">
-        <v>3.803707830852335</v>
+        <v>3.828605874844319</v>
       </c>
       <c r="H82" t="n">
-        <v>3.263157840084152</v>
+        <v>3.285717623432144</v>
       </c>
       <c r="I82" t="n">
-        <v>2.773798509277275</v>
+        <v>2.80613161063523</v>
       </c>
       <c r="J82" t="n">
         <v>1.339733461728624</v>
@@ -6682,19 +6682,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1.236544582600929</v>
+        <v>1.220232282319867</v>
       </c>
       <c r="F83" t="n">
-        <v>1.679788114806948</v>
+        <v>1.670985983968885</v>
       </c>
       <c r="G83" t="n">
-        <v>2.134127760291253</v>
+        <v>2.13437598310336</v>
       </c>
       <c r="H83" t="n">
-        <v>2.209146969140046</v>
+        <v>2.215794951286477</v>
       </c>
       <c r="I83" t="n">
-        <v>2.062808351531463</v>
+        <v>2.078206241891424</v>
       </c>
       <c r="J83" t="n">
         <v>1.289500359327421</v>
@@ -6910,58 +6910,58 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2.107194833201333</v>
+        <v>2.02581431370026</v>
       </c>
       <c r="F86" t="n">
-        <v>2.382788960599231</v>
+        <v>2.281769132994949</v>
       </c>
       <c r="G86" t="n">
-        <v>2.44625262010296</v>
+        <v>2.340462127113462</v>
       </c>
       <c r="H86" t="n">
-        <v>2.284458971912458</v>
+        <v>2.186650366748166</v>
       </c>
       <c r="I86" t="n">
-        <v>1.995220989036745</v>
+        <v>1.910536621979303</v>
       </c>
       <c r="J86" t="n">
-        <v>1.728995916721875</v>
+        <v>1.655806119916873</v>
       </c>
       <c r="K86" t="n">
-        <v>1.439070821793143</v>
+        <v>1.378075729969425</v>
       </c>
       <c r="L86" t="n">
-        <v>1.195371743808346</v>
+        <v>1.144211059935336</v>
       </c>
       <c r="M86" t="n">
-        <v>1.015516766196619</v>
+        <v>0.9701928890315354</v>
       </c>
       <c r="N86" t="n">
-        <v>0.8811288318133464</v>
+        <v>0.8381957939009033</v>
       </c>
       <c r="O86" t="n">
-        <v>0.7669085234517053</v>
+        <v>0.7255465332833667</v>
       </c>
       <c r="P86" t="n">
-        <v>0.6938685591561258</v>
+        <v>0.6532395449394012</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.6244764587568459</v>
+        <v>0.5860506358597454</v>
       </c>
       <c r="R86" t="n">
-        <v>0.5480927079236311</v>
+        <v>0.5136638459045059</v>
       </c>
       <c r="S86" t="n">
-        <v>0.4635305943626015</v>
+        <v>0.4343869443675727</v>
       </c>
       <c r="T86" t="n">
-        <v>0.3773738817661134</v>
+        <v>0.3539510243264289</v>
       </c>
       <c r="U86" t="n">
-        <v>0.3017684974702745</v>
+        <v>0.2833273657513241</v>
       </c>
       <c r="V86" t="n">
-        <v>0.2378067098875167</v>
+        <v>0.2233796360795646</v>
       </c>
     </row>
     <row r="87">
@@ -6986,58 +6986,58 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.486236649767369</v>
+        <v>1.52305924119172</v>
       </c>
       <c r="F87" t="n">
-        <v>1.624296308706722</v>
+        <v>1.684755160939807</v>
       </c>
       <c r="G87" t="n">
-        <v>1.658370759344987</v>
+        <v>1.747531418656963</v>
       </c>
       <c r="H87" t="n">
-        <v>1.540849521262385</v>
+        <v>1.643073691792458</v>
       </c>
       <c r="I87" t="n">
-        <v>1.333912564610681</v>
+        <v>1.433850646784482</v>
       </c>
       <c r="J87" t="n">
-        <v>1.143288420752341</v>
+        <v>1.235782394979134</v>
       </c>
       <c r="K87" t="n">
-        <v>0.9410099785224441</v>
+        <v>1.021029234727878</v>
       </c>
       <c r="L87" t="n">
-        <v>0.7730860299921073</v>
+        <v>0.8412078947786612</v>
       </c>
       <c r="M87" t="n">
-        <v>0.6497000236531121</v>
+        <v>0.7081062220752796</v>
       </c>
       <c r="N87" t="n">
-        <v>0.5574321167731654</v>
+        <v>0.6076223611060644</v>
       </c>
       <c r="O87" t="n">
-        <v>0.4802133241849277</v>
+        <v>0.5226721920957256</v>
       </c>
       <c r="P87" t="n">
-        <v>0.4308278363488875</v>
+        <v>0.4675764807102242</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.3852142004817193</v>
+        <v>0.4167755855687641</v>
       </c>
       <c r="R87" t="n">
-        <v>0.3360513133258143</v>
+        <v>0.3624884228003666</v>
       </c>
       <c r="S87" t="n">
-        <v>0.2820412290444009</v>
+        <v>0.3033959223562666</v>
       </c>
       <c r="T87" t="n">
-        <v>0.2273775273228207</v>
+        <v>0.2439197961684048</v>
       </c>
       <c r="U87" t="n">
-        <v>0.1792410545419345</v>
+        <v>0.1917147084830446</v>
       </c>
       <c r="V87" t="n">
-        <v>0.13826250664875</v>
+        <v>0.14736079617032</v>
       </c>
     </row>
     <row r="88">
@@ -7062,58 +7062,58 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2.233165960645302</v>
+        <v>2.409411349854078</v>
       </c>
       <c r="F88" t="n">
-        <v>2.184554697614246</v>
+        <v>2.312571183877356</v>
       </c>
       <c r="G88" t="n">
-        <v>2.142746868977734</v>
+        <v>2.195545202063544</v>
       </c>
       <c r="H88" t="n">
-        <v>1.982408184298962</v>
+        <v>1.988614389366641</v>
       </c>
       <c r="I88" t="n">
-        <v>1.727621231837567</v>
+        <v>1.717634538218499</v>
       </c>
       <c r="J88" t="n">
-        <v>1.492471531484708</v>
+        <v>1.481394350176584</v>
       </c>
       <c r="K88" t="n">
-        <v>1.237549559110732</v>
+        <v>1.228961748175066</v>
       </c>
       <c r="L88" t="n">
-        <v>1.023852762970566</v>
+        <v>1.017447438996126</v>
       </c>
       <c r="M88" t="n">
-        <v>0.8651180349405347</v>
+        <v>0.8604396647135284</v>
       </c>
       <c r="N88" t="n">
-        <v>0.7443640121578574</v>
+        <v>0.7414540109654334</v>
       </c>
       <c r="O88" t="n">
-        <v>0.6414752128799983</v>
+        <v>0.640337371816913</v>
       </c>
       <c r="P88" t="n">
-        <v>0.5753464308561227</v>
+        <v>0.5755089945133752</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.5145422957418376</v>
+        <v>0.5156208853501312</v>
       </c>
       <c r="R88" t="n">
-        <v>0.4495199305568773</v>
+        <v>0.4512282876461247</v>
       </c>
       <c r="S88" t="n">
-        <v>0.3785943107825115</v>
+        <v>0.3804770249614501</v>
       </c>
       <c r="T88" t="n">
-        <v>0.3067111524319944</v>
+        <v>0.3086334319712036</v>
       </c>
       <c r="U88" t="n">
-        <v>0.243202262825178</v>
+        <v>0.245227972438059</v>
       </c>
       <c r="V88" t="n">
-        <v>0.1888707188054957</v>
+        <v>0.190912015050235</v>
       </c>
     </row>
     <row r="89">
@@ -7138,58 +7138,58 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3.334158790028663</v>
+        <v>3.593357430981193</v>
       </c>
       <c r="F89" t="n">
-        <v>3.37947292315073</v>
+        <v>3.642986533199285</v>
       </c>
       <c r="G89" t="n">
-        <v>3.355718701817087</v>
+        <v>3.612802677589262</v>
       </c>
       <c r="H89" t="n">
-        <v>3.070765748774047</v>
+        <v>3.306529649570011</v>
       </c>
       <c r="I89" t="n">
-        <v>2.634973396103816</v>
+        <v>2.83778979244057</v>
       </c>
       <c r="J89" t="n">
-        <v>2.245087210127935</v>
+        <v>2.414354611279172</v>
       </c>
       <c r="K89" t="n">
-        <v>1.841251062602232</v>
+        <v>1.97415306382365</v>
       </c>
       <c r="L89" t="n">
-        <v>1.510767842702802</v>
+        <v>1.615228575944171</v>
       </c>
       <c r="M89" t="n">
-        <v>1.270262853453146</v>
+        <v>1.356628219368675</v>
       </c>
       <c r="N89" t="n">
-        <v>1.091169807478555</v>
+        <v>1.166237667064941</v>
       </c>
       <c r="O89" t="n">
-        <v>0.9413457297424674</v>
+        <v>1.007681091677771</v>
       </c>
       <c r="P89" t="n">
-        <v>0.845973576988662</v>
+        <v>0.9070082080921252</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.7577392318618367</v>
+        <v>0.8137802694660533</v>
       </c>
       <c r="R89" t="n">
-        <v>0.662211183733211</v>
+        <v>0.7128041121704867</v>
       </c>
       <c r="S89" t="n">
-        <v>0.5566936237136859</v>
+        <v>0.6014864961959429</v>
       </c>
       <c r="T89" t="n">
-        <v>0.4491074359400392</v>
+        <v>0.4874595256138531</v>
       </c>
       <c r="U89" t="n">
-        <v>0.3534819504032773</v>
+        <v>0.3854276140901841</v>
       </c>
       <c r="V89" t="n">
-        <v>0.2711864975420568</v>
+        <v>0.2970114664875107</v>
       </c>
     </row>
     <row r="90">
@@ -7214,58 +7214,58 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1.419086398356073</v>
+        <v>1.382724928117704</v>
       </c>
       <c r="F90" t="n">
-        <v>1.603267375551329</v>
+        <v>1.530815345466796</v>
       </c>
       <c r="G90" t="n">
-        <v>1.647102565185459</v>
+        <v>1.570895038869724</v>
       </c>
       <c r="H90" t="n">
-        <v>1.533350639344628</v>
+        <v>1.469544414060857</v>
       </c>
       <c r="I90" t="n">
-        <v>1.333517472668247</v>
+        <v>1.284755714535351</v>
       </c>
       <c r="J90" t="n">
-        <v>1.15166983075686</v>
+        <v>1.113066238655402</v>
       </c>
       <c r="K90" t="n">
-        <v>0.9556052176911307</v>
+        <v>0.9256471007697158</v>
       </c>
       <c r="L90" t="n">
-        <v>0.7908203552003186</v>
+        <v>0.7677424622423181</v>
       </c>
       <c r="M90" t="n">
-        <v>0.6678569204101483</v>
+        <v>0.6500035505812755</v>
       </c>
       <c r="N90" t="n">
-        <v>0.574522828287113</v>
+        <v>0.5603218967655673</v>
       </c>
       <c r="O90" t="n">
-        <v>0.4953443687789248</v>
+        <v>0.4837719328274557</v>
       </c>
       <c r="P90" t="n">
-        <v>0.4446287402145641</v>
+        <v>0.4345625596721768</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.398047217837028</v>
+        <v>0.3891778164470405</v>
       </c>
       <c r="R90" t="n">
-        <v>0.3483102112234474</v>
+        <v>0.3405780601335762</v>
       </c>
       <c r="S90" t="n">
-        <v>0.2939169610747514</v>
+        <v>0.2874346195410649</v>
       </c>
       <c r="T90" t="n">
-        <v>0.2386365044870665</v>
+        <v>0.2335524609998202</v>
       </c>
       <c r="U90" t="n">
-        <v>0.1899990912632798</v>
+        <v>0.1860993573037886</v>
       </c>
       <c r="V90" t="n">
-        <v>0.1486659909182983</v>
+        <v>0.1456270130882713</v>
       </c>
     </row>
     <row r="91">
@@ -7290,58 +7290,58 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1.344988818052979</v>
+        <v>1.276068173439024</v>
       </c>
       <c r="F91" t="n">
-        <v>1.536978287920021</v>
+        <v>1.445158660360765</v>
       </c>
       <c r="G91" t="n">
-        <v>1.583387937633455</v>
+        <v>1.487023085290681</v>
       </c>
       <c r="H91" t="n">
-        <v>1.489538553053948</v>
+        <v>1.392595137145572</v>
       </c>
       <c r="I91" t="n">
-        <v>1.31842474924855</v>
+        <v>1.222384497645239</v>
       </c>
       <c r="J91" t="n">
-        <v>1.164660815265116</v>
+        <v>1.068350959655308</v>
       </c>
       <c r="K91" t="n">
-        <v>0.991278733761246</v>
+        <v>0.8995984479269846</v>
       </c>
       <c r="L91" t="n">
-        <v>0.8407660720020224</v>
+        <v>0.7564581430641818</v>
       </c>
       <c r="M91" t="n">
-        <v>0.7234777443001188</v>
+        <v>0.6475557925095298</v>
       </c>
       <c r="N91" t="n">
-        <v>0.6281062259223134</v>
+        <v>0.5612773894355936</v>
       </c>
       <c r="O91" t="n">
-        <v>0.5423995540704744</v>
+        <v>0.4849049469438503</v>
       </c>
       <c r="P91" t="n">
-        <v>0.485696787397668</v>
+        <v>0.4348167510616253</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.4333678406672206</v>
+        <v>0.3886668581432114</v>
       </c>
       <c r="R91" t="n">
-        <v>0.3781427584786323</v>
+        <v>0.3398606786136926</v>
       </c>
       <c r="S91" t="n">
-        <v>0.3180227887479222</v>
+        <v>0.2868250013887761</v>
       </c>
       <c r="T91" t="n">
-        <v>0.2577982428272079</v>
+        <v>0.2334622123736382</v>
       </c>
       <c r="U91" t="n">
-        <v>0.2057850959172443</v>
+        <v>0.1870483234785729</v>
       </c>
       <c r="V91" t="n">
-        <v>0.1621820276854871</v>
+        <v>0.1478897437619813</v>
       </c>
     </row>
     <row r="92">
@@ -7366,58 +7366,58 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1.32387024616698</v>
+        <v>1.196324441374812</v>
       </c>
       <c r="F92" t="n">
-        <v>1.547667939332442</v>
+        <v>1.390223740016109</v>
       </c>
       <c r="G92" t="n">
-        <v>1.578214097871265</v>
+        <v>1.4348482221471</v>
       </c>
       <c r="H92" t="n">
-        <v>1.470734801777914</v>
+        <v>1.34561680799354</v>
       </c>
       <c r="I92" t="n">
-        <v>1.292722047957208</v>
+        <v>1.182090869577015</v>
       </c>
       <c r="J92" t="n">
-        <v>1.135345263328244</v>
+        <v>1.032836559630183</v>
       </c>
       <c r="K92" t="n">
-        <v>0.9608654488690158</v>
+        <v>0.8683749731463419</v>
       </c>
       <c r="L92" t="n">
-        <v>0.8112596629775874</v>
+        <v>0.7288359935487458</v>
       </c>
       <c r="M92" t="n">
-        <v>0.6952180060464634</v>
+        <v>0.6225960709482372</v>
       </c>
       <c r="N92" t="n">
-        <v>0.6025271377493211</v>
+        <v>0.5391211312846333</v>
       </c>
       <c r="O92" t="n">
-        <v>0.5204095737460229</v>
+        <v>0.4658098652006741</v>
       </c>
       <c r="P92" t="n">
-        <v>0.4665787187656568</v>
+        <v>0.417979304193147</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.416632965195654</v>
+        <v>0.3737769080234833</v>
       </c>
       <c r="R92" t="n">
-        <v>0.3636395453318229</v>
+        <v>0.3268888200026571</v>
       </c>
       <c r="S92" t="n">
-        <v>0.3062199003854414</v>
+        <v>0.2760702064178747</v>
       </c>
       <c r="T92" t="n">
-        <v>0.2487109725689805</v>
+        <v>0.2249491883841664</v>
       </c>
       <c r="U92" t="n">
-        <v>0.1991827524008913</v>
+        <v>0.180576006873368</v>
       </c>
       <c r="V92" t="n">
-        <v>0.1574381224421059</v>
+        <v>0.1430551584448559</v>
       </c>
     </row>
     <row r="93">
@@ -7442,58 +7442,58 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1.072578384985504</v>
+        <v>1.07328492733212</v>
       </c>
       <c r="F93" t="n">
-        <v>1.183704787277133</v>
+        <v>1.186947535071903</v>
       </c>
       <c r="G93" t="n">
-        <v>1.206175312469988</v>
+        <v>1.228401498209557</v>
       </c>
       <c r="H93" t="n">
-        <v>1.121998371535533</v>
+        <v>1.164995746887495</v>
       </c>
       <c r="I93" t="n">
-        <v>0.9764703474529441</v>
+        <v>1.031995961277383</v>
       </c>
       <c r="J93" t="n">
-        <v>0.8420085983579969</v>
+        <v>0.9023707162404799</v>
       </c>
       <c r="K93" t="n">
-        <v>0.6961915646659785</v>
+        <v>0.7533733962542398</v>
       </c>
       <c r="L93" t="n">
-        <v>0.5733449046532569</v>
+        <v>0.6242563793899861</v>
       </c>
       <c r="M93" t="n">
-        <v>0.4820384670045952</v>
+        <v>0.5260860296555971</v>
       </c>
       <c r="N93" t="n">
-        <v>0.4132839459729286</v>
+        <v>0.4506017878803224</v>
       </c>
       <c r="O93" t="n">
-        <v>0.3556721492552769</v>
+        <v>0.3864226417513382</v>
       </c>
       <c r="P93" t="n">
-        <v>0.3188809169855569</v>
+        <v>0.344796496977402</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.2850869133806181</v>
+        <v>0.306960945415982</v>
       </c>
       <c r="R93" t="n">
-        <v>0.2487624782300554</v>
+        <v>0.2668569419339952</v>
       </c>
       <c r="S93" t="n">
-        <v>0.2088837727183104</v>
+        <v>0.2232309583734444</v>
       </c>
       <c r="T93" t="n">
-        <v>0.1685686812252457</v>
+        <v>0.1794242322117064</v>
       </c>
       <c r="U93" t="n">
-        <v>0.1331232087879936</v>
+        <v>0.1410859981248379</v>
       </c>
       <c r="V93" t="n">
-        <v>0.1029801431647977</v>
+        <v>0.1086211669620804</v>
       </c>
     </row>
     <row r="94">
@@ -7518,58 +7518,58 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1.94308695220196</v>
+        <v>2.021687800828235</v>
       </c>
       <c r="F94" t="n">
-        <v>2.105077252270249</v>
+        <v>2.21949819490464</v>
       </c>
       <c r="G94" t="n">
-        <v>2.122743869277008</v>
+        <v>2.248226156280381</v>
       </c>
       <c r="H94" t="n">
-        <v>1.952010042381795</v>
+        <v>2.069120276288171</v>
       </c>
       <c r="I94" t="n">
-        <v>1.679588757823143</v>
+        <v>1.778564330448094</v>
       </c>
       <c r="J94" t="n">
-        <v>1.436484920821536</v>
+        <v>1.519278080511072</v>
       </c>
       <c r="K94" t="n">
-        <v>1.182757501119873</v>
+        <v>1.250016179694362</v>
       </c>
       <c r="L94" t="n">
-        <v>0.9731142519960555</v>
+        <v>1.027978697781905</v>
       </c>
       <c r="M94" t="n">
-        <v>0.8192281269538942</v>
+        <v>0.8646505908687362</v>
       </c>
       <c r="N94" t="n">
-        <v>0.7040508630266772</v>
+        <v>0.7420788061197903</v>
       </c>
       <c r="O94" t="n">
-        <v>0.607386634379911</v>
+        <v>0.6391030323670878</v>
       </c>
       <c r="P94" t="n">
-        <v>0.5457386839364068</v>
+        <v>0.5731616518914423</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.4887681753303001</v>
+        <v>0.5122808287929409</v>
       </c>
       <c r="R94" t="n">
-        <v>0.4273100628832681</v>
+        <v>0.4469001825643266</v>
       </c>
       <c r="S94" t="n">
-        <v>0.3596954298651742</v>
+        <v>0.3753529086273444</v>
       </c>
       <c r="T94" t="n">
-        <v>0.2911604647397162</v>
+        <v>0.3029558985382429</v>
       </c>
       <c r="U94" t="n">
-        <v>0.2307453814908882</v>
+        <v>0.2393919306622516</v>
       </c>
       <c r="V94" t="n">
-        <v>0.1791473712442285</v>
+        <v>0.1853515301394829</v>
       </c>
     </row>
     <row r="95">
@@ -7594,58 +7594,58 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1.632961648487236</v>
+        <v>1.426675848707491</v>
       </c>
       <c r="F95" t="n">
-        <v>1.876373881662452</v>
+        <v>1.665495603926425</v>
       </c>
       <c r="G95" t="n">
-        <v>1.885003941181267</v>
+        <v>1.712202935006338</v>
       </c>
       <c r="H95" t="n">
-        <v>1.731816814722582</v>
+        <v>1.600818242449909</v>
       </c>
       <c r="I95" t="n">
-        <v>1.49734020125305</v>
+        <v>1.400136760760919</v>
       </c>
       <c r="J95" t="n">
-        <v>1.290809185124102</v>
+        <v>1.214616699522834</v>
       </c>
       <c r="K95" t="n">
-        <v>1.072025339933385</v>
+        <v>1.01169467468239</v>
       </c>
       <c r="L95" t="n">
-        <v>0.88974405467928</v>
+        <v>0.8406301214183998</v>
       </c>
       <c r="M95" t="n">
-        <v>0.7536404909531083</v>
+        <v>0.7127430465415335</v>
       </c>
       <c r="N95" t="n">
-        <v>0.649338737661619</v>
+        <v>0.6148282685207397</v>
       </c>
       <c r="O95" t="n">
-        <v>0.5599425697520612</v>
+        <v>0.5307960817036165</v>
       </c>
       <c r="P95" t="n">
-        <v>0.5020899953747289</v>
+        <v>0.4765611358924599</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.4490510267106012</v>
+        <v>0.4266567479333437</v>
       </c>
       <c r="R95" t="n">
-        <v>0.3926814747003181</v>
+        <v>0.3734405058796125</v>
       </c>
       <c r="S95" t="n">
-        <v>0.3314748713896906</v>
+        <v>0.3154700328801892</v>
       </c>
       <c r="T95" t="n">
-        <v>0.269239174950317</v>
+        <v>0.2566762100860795</v>
       </c>
       <c r="U95" t="n">
-        <v>0.2148928483142863</v>
+        <v>0.2050809104565594</v>
       </c>
       <c r="V95" t="n">
-        <v>0.1685811953061192</v>
+        <v>0.1610889148036976</v>
       </c>
     </row>
     <row r="96">
@@ -7670,58 +7670,58 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1.539843059568445</v>
+        <v>1.594688181105587</v>
       </c>
       <c r="F96" t="n">
-        <v>1.6296511779829</v>
+        <v>1.647795582721886</v>
       </c>
       <c r="G96" t="n">
-        <v>1.664721822355264</v>
+        <v>1.623148995788641</v>
       </c>
       <c r="H96" t="n">
-        <v>1.578808091067011</v>
+        <v>1.501715737318408</v>
       </c>
       <c r="I96" t="n">
-        <v>1.398166162930376</v>
+        <v>1.3137668985143</v>
       </c>
       <c r="J96" t="n">
-        <v>1.219815979609918</v>
+        <v>1.141959483025026</v>
       </c>
       <c r="K96" t="n">
-        <v>1.017849671001548</v>
+        <v>0.9525600110276862</v>
       </c>
       <c r="L96" t="n">
-        <v>0.8458199796599832</v>
+        <v>0.7921177538690098</v>
       </c>
       <c r="M96" t="n">
-        <v>0.7169252421697653</v>
+        <v>0.6719697738695144</v>
       </c>
       <c r="N96" t="n">
-        <v>0.6177765889828072</v>
+        <v>0.579757970543005</v>
       </c>
       <c r="O96" t="n">
-        <v>0.5321906167338555</v>
+        <v>0.500338660080913</v>
       </c>
       <c r="P96" t="n">
-        <v>0.4766170156273845</v>
+        <v>0.4489898307455231</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.4256531901478755</v>
+        <v>0.4017644670058306</v>
       </c>
       <c r="R96" t="n">
-        <v>0.3718715742396118</v>
+        <v>0.3515589644015404</v>
       </c>
       <c r="S96" t="n">
-        <v>0.3134663753823888</v>
+        <v>0.2968901717345103</v>
       </c>
       <c r="T96" t="n">
-        <v>0.2547767296815057</v>
+        <v>0.2416571079641335</v>
       </c>
       <c r="U96" t="n">
-        <v>0.2033555184008566</v>
+        <v>0.1931481488819423</v>
       </c>
       <c r="V96" t="n">
-        <v>0.1596015727165428</v>
+        <v>0.1518153083934728</v>
       </c>
     </row>
     <row r="97">
@@ -7746,58 +7746,58 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1.614988520461812</v>
+        <v>1.708997937115627</v>
       </c>
       <c r="F97" t="n">
-        <v>1.631741901491667</v>
+        <v>1.661954236645777</v>
       </c>
       <c r="G97" t="n">
-        <v>1.663884637111802</v>
+        <v>1.618088270799003</v>
       </c>
       <c r="H97" t="n">
-        <v>1.584471459395251</v>
+        <v>1.498329555139031</v>
       </c>
       <c r="I97" t="n">
-        <v>1.404319738761834</v>
+        <v>1.312667828924116</v>
       </c>
       <c r="J97" t="n">
-        <v>1.224704210098822</v>
+        <v>1.141575741166915</v>
       </c>
       <c r="K97" t="n">
-        <v>1.021974169782788</v>
+        <v>0.9525417085180919</v>
       </c>
       <c r="L97" t="n">
-        <v>0.8497327588029285</v>
+        <v>0.7924185944909908</v>
       </c>
       <c r="M97" t="n">
-        <v>0.7203997948650802</v>
+        <v>0.6723781465841762</v>
       </c>
       <c r="N97" t="n">
-        <v>0.6208298936794872</v>
+        <v>0.5801659267348314</v>
       </c>
       <c r="O97" t="n">
-        <v>0.5350979838852342</v>
+        <v>0.5007706161391009</v>
       </c>
       <c r="P97" t="n">
-        <v>0.4797936164177056</v>
+        <v>0.4495334372483107</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.4286143267078928</v>
+        <v>0.4022598319169655</v>
       </c>
       <c r="R97" t="n">
-        <v>0.3740814574324606</v>
+        <v>0.3518674135509796</v>
       </c>
       <c r="S97" t="n">
-        <v>0.3149112051576158</v>
+        <v>0.2970335798758059</v>
       </c>
       <c r="T97" t="n">
-        <v>0.2554824703215428</v>
+        <v>0.2416461258458455</v>
       </c>
       <c r="U97" t="n">
-        <v>0.203410022167144</v>
+        <v>0.1929777833128722</v>
       </c>
       <c r="V97" t="n">
-        <v>0.1592500254708857</v>
+        <v>0.1515273459616202</v>
       </c>
     </row>
     <row r="98">
@@ -7822,58 +7822,58 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1.873584870206801</v>
+        <v>1.889597205109541</v>
       </c>
       <c r="F98" t="n">
-        <v>1.873019711153435</v>
+        <v>1.880880358628159</v>
       </c>
       <c r="G98" t="n">
-        <v>1.863423093669387</v>
+        <v>1.861154297042623</v>
       </c>
       <c r="H98" t="n">
-        <v>1.77165626786888</v>
+        <v>1.762270023827197</v>
       </c>
       <c r="I98" t="n">
-        <v>1.602365431553695</v>
+        <v>1.589277913739827</v>
       </c>
       <c r="J98" t="n">
-        <v>1.386204552214799</v>
+        <v>1.37223818532698</v>
       </c>
       <c r="K98" t="n">
-        <v>1.154033788257695</v>
+        <v>1.140909116427454</v>
       </c>
       <c r="L98" t="n">
-        <v>0.95857992382269</v>
+        <v>0.9468138975280415</v>
       </c>
       <c r="M98" t="n">
-        <v>0.8221116203042326</v>
+        <v>0.8114798176805066</v>
       </c>
       <c r="N98" t="n">
-        <v>0.7338112055434226</v>
+        <v>0.7239664567095643</v>
       </c>
       <c r="O98" t="n">
-        <v>0.6623975856804876</v>
+        <v>0.6532771804167481</v>
       </c>
       <c r="P98" t="n">
-        <v>0.6234950486058131</v>
+        <v>0.6147579711315494</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.5960065473595557</v>
+        <v>0.5875255693299684</v>
       </c>
       <c r="R98" t="n">
-        <v>0.5627914636988182</v>
+        <v>0.5546801150538568</v>
       </c>
       <c r="S98" t="n">
-        <v>0.5158981070151714</v>
+        <v>0.5083941060654905</v>
       </c>
       <c r="T98" t="n">
-        <v>0.4601151900897683</v>
+        <v>0.453353805514656</v>
       </c>
       <c r="U98" t="n">
-        <v>0.4047923811500958</v>
+        <v>0.398789927751921</v>
       </c>
       <c r="V98" t="n">
-        <v>0.3545647747168141</v>
+        <v>0.3492687800137833</v>
       </c>
     </row>
     <row r="99">
@@ -7898,58 +7898,58 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2.080916193961408</v>
+        <v>2.105503913028885</v>
       </c>
       <c r="F99" t="n">
-        <v>1.952861574654208</v>
+        <v>1.98313989478992</v>
       </c>
       <c r="G99" t="n">
-        <v>1.781758244215204</v>
+        <v>1.81477431815602</v>
       </c>
       <c r="H99" t="n">
-        <v>1.583050185445173</v>
+        <v>1.615576388743373</v>
       </c>
       <c r="I99" t="n">
-        <v>1.372309182284578</v>
+        <v>1.401922000968485</v>
       </c>
       <c r="J99" t="n">
-        <v>1.161594876248719</v>
+        <v>1.186993111923061</v>
       </c>
       <c r="K99" t="n">
-        <v>0.958743873746414</v>
+        <v>0.9795313953397482</v>
       </c>
       <c r="L99" t="n">
-        <v>0.7959974742346648</v>
+        <v>0.8129158872632</v>
       </c>
       <c r="M99" t="n">
-        <v>0.6862443169068914</v>
+        <v>0.7004636831714182</v>
       </c>
       <c r="N99" t="n">
-        <v>0.6182544900880412</v>
+        <v>0.6307305932349759</v>
       </c>
       <c r="O99" t="n">
-        <v>0.5653361392208173</v>
+        <v>0.5764500887514411</v>
       </c>
       <c r="P99" t="n">
-        <v>0.5400843416184065</v>
+        <v>0.550467088181137</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.524047738206476</v>
+        <v>0.533919092100429</v>
       </c>
       <c r="R99" t="n">
-        <v>0.5028978205081867</v>
+        <v>0.5121714678136408</v>
       </c>
       <c r="S99" t="n">
-        <v>0.4700593516791891</v>
+        <v>0.4785051616305138</v>
       </c>
       <c r="T99" t="n">
-        <v>0.4279903019410022</v>
+        <v>0.4354799521976144</v>
       </c>
       <c r="U99" t="n">
-        <v>0.3845369917070928</v>
+        <v>0.3910907620870236</v>
       </c>
       <c r="V99" t="n">
-        <v>0.3441444446540762</v>
+        <v>0.3498437446936966</v>
       </c>
     </row>
     <row r="100">
@@ -7974,58 +7974,58 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1.78593078873895</v>
+        <v>1.782725378845138</v>
       </c>
       <c r="F100" t="n">
-        <v>1.962284185670105</v>
+        <v>1.949231275101339</v>
       </c>
       <c r="G100" t="n">
-        <v>2.026607048535957</v>
+        <v>2.005089202253425</v>
       </c>
       <c r="H100" t="n">
-        <v>1.947309216458717</v>
+        <v>1.921151738073213</v>
       </c>
       <c r="I100" t="n">
-        <v>1.760464318660638</v>
+        <v>1.733281265840135</v>
       </c>
       <c r="J100" t="n">
-        <v>1.518222978497781</v>
+        <v>1.492631784997846</v>
       </c>
       <c r="K100" t="n">
-        <v>1.258727910351439</v>
+        <v>1.236231127738356</v>
       </c>
       <c r="L100" t="n">
-        <v>1.04233062824516</v>
+        <v>1.022880756237192</v>
       </c>
       <c r="M100" t="n">
-        <v>0.8917588303283011</v>
+        <v>0.8745382223532039</v>
       </c>
       <c r="N100" t="n">
-        <v>0.7934568049450949</v>
+        <v>0.7777250610515518</v>
       </c>
       <c r="O100" t="n">
-        <v>0.7129666302775083</v>
+        <v>0.6985489662187619</v>
       </c>
       <c r="P100" t="n">
-        <v>0.6668688887447776</v>
+        <v>0.653213415325112</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.6318405070454658</v>
+        <v>0.6188197306081168</v>
       </c>
       <c r="R100" t="n">
-        <v>0.5905264460958395</v>
+        <v>0.5783298048718947</v>
       </c>
       <c r="S100" t="n">
-        <v>0.5369298141606872</v>
+        <v>0.5257811492252027</v>
       </c>
       <c r="T100" t="n">
-        <v>0.4751313542024994</v>
+        <v>0.4652001828594984</v>
       </c>
       <c r="U100" t="n">
-        <v>0.4145033142300262</v>
+        <v>0.4058044707092466</v>
       </c>
       <c r="V100" t="n">
-        <v>0.3603067945742836</v>
+        <v>0.3527154205153401</v>
       </c>
     </row>
     <row r="101">
@@ -8050,58 +8050,58 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2.106001552047194</v>
+        <v>2.11807117244989</v>
       </c>
       <c r="F101" t="n">
-        <v>2.089077209103628</v>
+        <v>2.098390788474151</v>
       </c>
       <c r="G101" t="n">
-        <v>1.981841426836564</v>
+        <v>1.987366695173188</v>
       </c>
       <c r="H101" t="n">
-        <v>1.797202993147077</v>
+        <v>1.799565959577222</v>
       </c>
       <c r="I101" t="n">
-        <v>1.571239151478019</v>
+        <v>1.57128215850272</v>
       </c>
       <c r="J101" t="n">
-        <v>1.333548999400886</v>
+        <v>1.33213391401936</v>
       </c>
       <c r="K101" t="n">
-        <v>1.100953205962987</v>
+        <v>1.098738630720973</v>
       </c>
       <c r="L101" t="n">
-        <v>0.9135627669049304</v>
+        <v>0.9109341903280269</v>
       </c>
       <c r="M101" t="n">
-        <v>0.7863500818745834</v>
+        <v>0.7834591086759431</v>
       </c>
       <c r="N101" t="n">
-        <v>0.7057526608842856</v>
+        <v>0.7027019252346864</v>
       </c>
       <c r="O101" t="n">
-        <v>0.6410803271304348</v>
+        <v>0.6380045268393393</v>
       </c>
       <c r="P101" t="n">
-        <v>0.6067392080908305</v>
+        <v>0.6036755073579724</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.5825124383310395</v>
+        <v>0.5794955167215436</v>
       </c>
       <c r="R101" t="n">
-        <v>0.5526917742192508</v>
+        <v>0.5497767960823013</v>
       </c>
       <c r="S101" t="n">
-        <v>0.5104883190369041</v>
+        <v>0.5076977621404786</v>
       </c>
       <c r="T101" t="n">
-        <v>0.4587303967041788</v>
+        <v>0.4561371153841239</v>
       </c>
       <c r="U101" t="n">
-        <v>0.4065268999901896</v>
+        <v>0.4041670006796065</v>
       </c>
       <c r="V101" t="n">
-        <v>0.3588033278472519</v>
+        <v>0.3566639279216534</v>
       </c>
     </row>
     <row r="102">
@@ -8126,58 +8126,58 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1.675781121703732</v>
+        <v>1.666877244895313</v>
       </c>
       <c r="F102" t="n">
-        <v>1.702070066623367</v>
+        <v>1.696328917747532</v>
       </c>
       <c r="G102" t="n">
-        <v>1.55860084347827</v>
+        <v>1.556401268625192</v>
       </c>
       <c r="H102" t="n">
-        <v>1.360009256337613</v>
+        <v>1.360265262924904</v>
       </c>
       <c r="I102" t="n">
-        <v>1.153957131017907</v>
+        <v>1.155506154691588</v>
       </c>
       <c r="J102" t="n">
-        <v>0.9593158973451666</v>
+        <v>0.9613188261989595</v>
       </c>
       <c r="K102" t="n">
-        <v>0.7808409480404601</v>
+        <v>0.7828047379668219</v>
       </c>
       <c r="L102" t="n">
-        <v>0.6413560616942922</v>
+        <v>0.6431075455124432</v>
       </c>
       <c r="M102" t="n">
-        <v>0.5482204197545757</v>
+        <v>0.5497301075681541</v>
       </c>
       <c r="N102" t="n">
-        <v>0.4903907658543767</v>
+        <v>0.4916826068988827</v>
       </c>
       <c r="O102" t="n">
-        <v>0.4452165056170606</v>
+        <v>0.4463248170900405</v>
       </c>
       <c r="P102" t="n">
-        <v>0.42241543127232</v>
+        <v>0.423394417384108</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.4071311691245082</v>
+        <v>0.4080008921086543</v>
       </c>
       <c r="R102" t="n">
-        <v>0.3879208573091966</v>
+        <v>0.3886867919687745</v>
       </c>
       <c r="S102" t="n">
-        <v>0.3595717462714695</v>
+        <v>0.3602347441135708</v>
       </c>
       <c r="T102" t="n">
-        <v>0.3244531465897433</v>
+        <v>0.3250009582297026</v>
       </c>
       <c r="U102" t="n">
-        <v>0.2888716390758335</v>
+        <v>0.2893071753478108</v>
       </c>
       <c r="V102" t="n">
-        <v>0.2561721643040427</v>
+        <v>0.2565069144662047</v>
       </c>
     </row>
     <row r="103">
@@ -8202,58 +8202,58 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2.357973243413858</v>
+        <v>2.373832647488285</v>
       </c>
       <c r="F103" t="n">
-        <v>2.418623254230762</v>
+        <v>2.421645748006634</v>
       </c>
       <c r="G103" t="n">
-        <v>2.454296690315208</v>
+        <v>2.443518523343991</v>
       </c>
       <c r="H103" t="n">
-        <v>2.354731214645616</v>
+        <v>2.335205143829797</v>
       </c>
       <c r="I103" t="n">
-        <v>2.128474093966688</v>
+        <v>2.105493679755466</v>
       </c>
       <c r="J103" t="n">
-        <v>1.83054228985187</v>
+        <v>1.808007832943721</v>
       </c>
       <c r="K103" t="n">
-        <v>1.509325314051094</v>
+        <v>1.48945896282613</v>
       </c>
       <c r="L103" t="n">
-        <v>1.239546201671396</v>
+        <v>1.222702620886856</v>
       </c>
       <c r="M103" t="n">
-        <v>1.050874819960773</v>
+        <v>1.036409809278415</v>
       </c>
       <c r="N103" t="n">
-        <v>0.9284848636082476</v>
+        <v>0.9156668095865126</v>
       </c>
       <c r="O103" t="n">
-        <v>0.8311965492778283</v>
+        <v>0.8197487740065315</v>
       </c>
       <c r="P103" t="n">
-        <v>0.7769593510440869</v>
+        <v>0.7663442074829462</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.7372167385685684</v>
+        <v>0.7272920407698727</v>
       </c>
       <c r="R103" t="n">
-        <v>0.6907910109315596</v>
+        <v>0.6816981102585777</v>
       </c>
       <c r="S103" t="n">
-        <v>0.6291972309326066</v>
+        <v>0.6211308294178346</v>
       </c>
       <c r="T103" t="n">
-        <v>0.5580597675922154</v>
+        <v>0.5510961736989964</v>
       </c>
       <c r="U103" t="n">
-        <v>0.489074876032232</v>
+        <v>0.4831220105512685</v>
       </c>
       <c r="V103" t="n">
-        <v>0.4270251072065182</v>
+        <v>0.4219776292393956</v>
       </c>
     </row>
     <row r="104">
@@ -8278,58 +8278,58 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1.984076118274855</v>
+        <v>1.973163408618752</v>
       </c>
       <c r="F104" t="n">
-        <v>2.028070251797121</v>
+        <v>2.020084054241797</v>
       </c>
       <c r="G104" t="n">
-        <v>1.872997302468637</v>
+        <v>1.868223289180057</v>
       </c>
       <c r="H104" t="n">
-        <v>1.626260577292647</v>
+        <v>1.625139013367321</v>
       </c>
       <c r="I104" t="n">
-        <v>1.367690213843308</v>
+        <v>1.369204609421004</v>
       </c>
       <c r="J104" t="n">
-        <v>1.127533093343601</v>
+        <v>1.130497560908378</v>
       </c>
       <c r="K104" t="n">
-        <v>0.912135134949381</v>
+        <v>0.9155798321637949</v>
       </c>
       <c r="L104" t="n">
-        <v>0.7462566943674976</v>
+        <v>0.7496725289355579</v>
       </c>
       <c r="M104" t="n">
-        <v>0.6362749066431495</v>
+        <v>0.6395074306541181</v>
       </c>
       <c r="N104" t="n">
-        <v>0.5683642393333408</v>
+        <v>0.5713919513142874</v>
       </c>
       <c r="O104" t="n">
-        <v>0.516150402130502</v>
+        <v>0.518904191109936</v>
       </c>
       <c r="P104" t="n">
-        <v>0.4901040067869361</v>
+        <v>0.4926706929451074</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.4730399292614182</v>
+        <v>0.4754107714092824</v>
       </c>
       <c r="R104" t="n">
-        <v>0.4516711125203474</v>
+        <v>0.4537820788160449</v>
       </c>
       <c r="S104" t="n">
-        <v>0.4197406426053586</v>
+        <v>0.4215395094206283</v>
       </c>
       <c r="T104" t="n">
-        <v>0.3795777628547438</v>
+        <v>0.3810687303463153</v>
       </c>
       <c r="U104" t="n">
-        <v>0.3385085697072933</v>
+        <v>0.339741877906634</v>
       </c>
       <c r="V104" t="n">
-        <v>0.300603733882498</v>
+        <v>0.3016262903932618</v>
       </c>
     </row>
     <row r="105">
@@ -8354,58 +8354,58 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1.985285087935222</v>
+        <v>1.996791842892897</v>
       </c>
       <c r="F105" t="n">
-        <v>1.969695578218501</v>
+        <v>1.97847497366597</v>
       </c>
       <c r="G105" t="n">
-        <v>1.842468253091405</v>
+        <v>1.850052615857936</v>
       </c>
       <c r="H105" t="n">
-        <v>1.647514841037438</v>
+        <v>1.653811807085575</v>
       </c>
       <c r="I105" t="n">
-        <v>1.428425653843074</v>
+        <v>1.433022895807845</v>
       </c>
       <c r="J105" t="n">
-        <v>1.210655631729616</v>
+        <v>1.213327787463969</v>
       </c>
       <c r="K105" t="n">
-        <v>1.001268721700586</v>
+        <v>1.002340460587406</v>
       </c>
       <c r="L105" t="n">
-        <v>0.8321129469126162</v>
+        <v>0.8321616673798546</v>
       </c>
       <c r="M105" t="n">
-        <v>0.7160954961806312</v>
+        <v>0.7155876041657843</v>
       </c>
       <c r="N105" t="n">
-        <v>0.6425335293023633</v>
+        <v>0.6417076804952199</v>
       </c>
       <c r="O105" t="n">
-        <v>0.5844773074181859</v>
+        <v>0.5834210481224598</v>
       </c>
       <c r="P105" t="n">
-        <v>0.5555947981390857</v>
+        <v>0.5542799552931185</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.5362146427928185</v>
+        <v>0.5346606608651341</v>
       </c>
       <c r="R105" t="n">
-        <v>0.5115621801929515</v>
+        <v>0.5098003008186379</v>
       </c>
       <c r="S105" t="n">
-        <v>0.4748720008766543</v>
+        <v>0.4729383163029491</v>
       </c>
       <c r="T105" t="n">
-        <v>0.428458881403378</v>
+        <v>0.4264775584516754</v>
       </c>
       <c r="U105" t="n">
-        <v>0.3808707176814011</v>
+        <v>0.3789407740347174</v>
       </c>
       <c r="V105" t="n">
-        <v>0.3369958635844953</v>
+        <v>0.3351484145441715</v>
       </c>
     </row>
     <row r="106">
@@ -8430,58 +8430,58 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1.956542038470582</v>
+        <v>1.943061421205716</v>
       </c>
       <c r="F106" t="n">
-        <v>1.952958055308895</v>
+        <v>1.946708089579805</v>
       </c>
       <c r="G106" t="n">
-        <v>1.736900772566628</v>
+        <v>1.73861636856</v>
       </c>
       <c r="H106" t="n">
-        <v>1.493044276037431</v>
+        <v>1.499394650279867</v>
       </c>
       <c r="I106" t="n">
-        <v>1.261867306689206</v>
+        <v>1.269972323435384</v>
       </c>
       <c r="J106" t="n">
-        <v>1.050820947921284</v>
+        <v>1.058821867276876</v>
       </c>
       <c r="K106" t="n">
-        <v>0.8586362151094926</v>
+        <v>0.8655933038935332</v>
       </c>
       <c r="L106" t="n">
-        <v>0.7085867412051544</v>
+        <v>0.7143324897687487</v>
       </c>
       <c r="M106" t="n">
-        <v>0.6082520929324248</v>
+        <v>0.6130368210115784</v>
       </c>
       <c r="N106" t="n">
-        <v>0.5459824195970253</v>
+        <v>0.5500823137151252</v>
       </c>
       <c r="O106" t="n">
-        <v>0.4972784514114096</v>
+        <v>0.5008345315723086</v>
       </c>
       <c r="P106" t="n">
-        <v>0.4731923476379574</v>
+        <v>0.4763959508731498</v>
       </c>
       <c r="Q106" t="n">
-        <v>0.4574498070975739</v>
+        <v>0.4603371831008612</v>
       </c>
       <c r="R106" t="n">
-        <v>0.437285352107488</v>
+        <v>0.4398236463259909</v>
       </c>
       <c r="S106" t="n">
-        <v>0.4066089105400499</v>
+        <v>0.4087966055423191</v>
       </c>
       <c r="T106" t="n">
-        <v>0.3678459623352965</v>
+        <v>0.3697066925860845</v>
       </c>
       <c r="U106" t="n">
-        <v>0.3281783245028504</v>
+        <v>0.3297673374572798</v>
       </c>
       <c r="V106" t="n">
-        <v>0.2915928296440399</v>
+        <v>0.2929516236668808</v>
       </c>
     </row>
     <row r="107">
@@ -8506,58 +8506,58 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2.590167753540089</v>
+        <v>2.685194382089434</v>
       </c>
       <c r="F107" t="n">
-        <v>2.200088732635796</v>
+        <v>2.298823956467231</v>
       </c>
       <c r="G107" t="n">
-        <v>1.944624058853597</v>
+        <v>2.034749900436824</v>
       </c>
       <c r="H107" t="n">
-        <v>1.711208877702511</v>
+        <v>1.790109062287533</v>
       </c>
       <c r="I107" t="n">
-        <v>1.483204423399052</v>
+        <v>1.550541394105357</v>
       </c>
       <c r="J107" t="n">
-        <v>1.261966229871569</v>
+        <v>1.31831670904231</v>
       </c>
       <c r="K107" t="n">
-        <v>1.050223950106316</v>
+        <v>1.096369670438957</v>
       </c>
       <c r="L107" t="n">
-        <v>0.8800699746147386</v>
+        <v>0.9181348910509876</v>
       </c>
       <c r="M107" t="n">
-        <v>0.765466045619377</v>
+        <v>0.7980223911828779</v>
       </c>
       <c r="N107" t="n">
-        <v>0.6947085903782443</v>
+        <v>0.723718191203259</v>
       </c>
       <c r="O107" t="n">
-        <v>0.6392795937797525</v>
+        <v>0.6654416587326775</v>
       </c>
       <c r="P107" t="n">
-        <v>0.6138506681224333</v>
+        <v>0.6384539510415761</v>
       </c>
       <c r="Q107" t="n">
-        <v>0.5983045822734001</v>
+        <v>0.6217798320474904</v>
       </c>
       <c r="R107" t="n">
-        <v>0.5764657103417589</v>
+        <v>0.5985700633561037</v>
       </c>
       <c r="S107" t="n">
-        <v>0.5409462172357408</v>
+        <v>0.5611279081062703</v>
       </c>
       <c r="T107" t="n">
-        <v>0.4942745130069016</v>
+        <v>0.5121544084616327</v>
       </c>
       <c r="U107" t="n">
-        <v>0.4454911748900882</v>
+        <v>0.4610894295785898</v>
       </c>
       <c r="V107" t="n">
-        <v>0.3998977639577651</v>
+        <v>0.4134228287567503</v>
       </c>
     </row>
     <row r="108">
@@ -8582,58 +8582,58 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2.027343418359165</v>
+        <v>2.062832230418746</v>
       </c>
       <c r="F108" t="n">
-        <v>1.86297635186022</v>
+        <v>1.897613890750061</v>
       </c>
       <c r="G108" t="n">
-        <v>1.713029581214218</v>
+        <v>1.74287796492631</v>
       </c>
       <c r="H108" t="n">
-        <v>1.532151009618736</v>
+        <v>1.557000443703341</v>
       </c>
       <c r="I108" t="n">
-        <v>1.330891417269783</v>
+        <v>1.351084794940341</v>
       </c>
       <c r="J108" t="n">
-        <v>1.125670146941986</v>
+        <v>1.141886036364998</v>
       </c>
       <c r="K108" t="n">
-        <v>0.9274161097216824</v>
+        <v>0.9402528114808119</v>
       </c>
       <c r="L108" t="n">
-        <v>0.7684475495414315</v>
+        <v>0.778745307157658</v>
       </c>
       <c r="M108" t="n">
-        <v>0.6611999931799194</v>
+        <v>0.6697757278498507</v>
       </c>
       <c r="N108" t="n">
-        <v>0.5945059380952358</v>
+        <v>0.6019637948350108</v>
       </c>
       <c r="O108" t="n">
-        <v>0.5424273253381359</v>
+        <v>0.5490000086217084</v>
       </c>
       <c r="P108" t="n">
-        <v>0.5169002260219333</v>
+        <v>0.5229820189681151</v>
       </c>
       <c r="Q108" t="n">
-        <v>0.5001444779948321</v>
+        <v>0.5059219919194697</v>
       </c>
       <c r="R108" t="n">
-        <v>0.4785424666820089</v>
+        <v>0.4839901167865719</v>
       </c>
       <c r="S108" t="n">
-        <v>0.4458597876607706</v>
+        <v>0.4508659404151662</v>
       </c>
       <c r="T108" t="n">
-        <v>0.4045548973777356</v>
+        <v>0.4090170417738715</v>
       </c>
       <c r="U108" t="n">
-        <v>0.3621999754184647</v>
+        <v>0.3660958402179632</v>
       </c>
       <c r="V108" t="n">
-        <v>0.3229927323970754</v>
+        <v>0.3263534760509903</v>
       </c>
     </row>
     <row r="109">
@@ -8658,58 +8658,58 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2.712624166446358</v>
+        <v>2.65498865793935</v>
       </c>
       <c r="F109" t="n">
-        <v>2.986859168986806</v>
+        <v>2.933408454408235</v>
       </c>
       <c r="G109" t="n">
-        <v>2.647099219270633</v>
+        <v>2.607629223081271</v>
       </c>
       <c r="H109" t="n">
-        <v>2.150780398755363</v>
+        <v>2.125734314324399</v>
       </c>
       <c r="I109" t="n">
-        <v>1.697331761547767</v>
+        <v>1.683541550769557</v>
       </c>
       <c r="J109" t="n">
-        <v>1.337753264020043</v>
+        <v>1.331073051502768</v>
       </c>
       <c r="K109" t="n">
-        <v>1.051277851128763</v>
+        <v>1.048608904569165</v>
       </c>
       <c r="L109" t="n">
-        <v>0.8450289177956923</v>
+        <v>0.8443457816493509</v>
       </c>
       <c r="M109" t="n">
-        <v>0.7128530595278398</v>
+        <v>0.7130608991527856</v>
       </c>
       <c r="N109" t="n">
-        <v>0.6324669368308645</v>
+        <v>0.6330523876673695</v>
       </c>
       <c r="O109" t="n">
-        <v>0.571541991617365</v>
+        <v>0.5722480601547075</v>
       </c>
       <c r="P109" t="n">
-        <v>0.5407149155273951</v>
+        <v>0.54145119293505</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.5199958402080594</v>
+        <v>0.5207403206185856</v>
       </c>
       <c r="R109" t="n">
-        <v>0.4950254456434621</v>
+        <v>0.4956957232994206</v>
       </c>
       <c r="S109" t="n">
-        <v>0.4591734523804117</v>
+        <v>0.4596575731290277</v>
       </c>
       <c r="T109" t="n">
-        <v>0.414502903710825</v>
+        <v>0.4148112541385099</v>
       </c>
       <c r="U109" t="n">
-        <v>0.3689093696397119</v>
+        <v>0.3691044025832991</v>
       </c>
       <c r="V109" t="n">
-        <v>0.3269222418413468</v>
+        <v>0.3270382381255001</v>
       </c>
     </row>
     <row r="110">
@@ -8734,58 +8734,58 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1.359103418626239</v>
+        <v>1.354491331657907</v>
       </c>
       <c r="F110" t="n">
-        <v>1.36503067724451</v>
+        <v>1.363251015979136</v>
       </c>
       <c r="G110" t="n">
-        <v>1.249043353985214</v>
+        <v>1.249927419113465</v>
       </c>
       <c r="H110" t="n">
-        <v>1.09735490454335</v>
+        <v>1.099468661359274</v>
       </c>
       <c r="I110" t="n">
-        <v>0.9410385467281011</v>
+        <v>0.9431940079841531</v>
       </c>
       <c r="J110" t="n">
-        <v>0.791307957748422</v>
+        <v>0.792904557688722</v>
       </c>
       <c r="K110" t="n">
-        <v>0.6515853125901525</v>
+        <v>0.6524299047345833</v>
       </c>
       <c r="L110" t="n">
-        <v>0.5409383786134799</v>
+        <v>0.541144741134256</v>
       </c>
       <c r="M110" t="n">
-        <v>0.4661025169717178</v>
+        <v>0.4658676565835872</v>
       </c>
       <c r="N110" t="n">
-        <v>0.4187215966370709</v>
+        <v>0.418222973923664</v>
       </c>
       <c r="O110" t="n">
-        <v>0.3808203196002813</v>
+        <v>0.3801755392074668</v>
       </c>
       <c r="P110" t="n">
-        <v>0.3614240958010091</v>
+        <v>0.360669482807317</v>
       </c>
       <c r="Q110" t="n">
-        <v>0.3483275033603395</v>
+        <v>0.3474687910787616</v>
       </c>
       <c r="R110" t="n">
-        <v>0.3319425874690565</v>
+        <v>0.3309871460531367</v>
       </c>
       <c r="S110" t="n">
-        <v>0.3075785470836975</v>
+        <v>0.3065689040426343</v>
       </c>
       <c r="T110" t="n">
-        <v>0.2771851987196847</v>
+        <v>0.2761721704346351</v>
       </c>
       <c r="U110" t="n">
-        <v>0.2463528403661887</v>
+        <v>0.2453635664802893</v>
       </c>
       <c r="V110" t="n">
-        <v>0.2180411721953869</v>
+        <v>0.2170813316156387</v>
       </c>
     </row>
     <row r="111">
@@ -8810,58 +8810,58 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1.917809338171851</v>
+        <v>1.905968946577835</v>
       </c>
       <c r="F111" t="n">
-        <v>1.952561808630212</v>
+        <v>1.944562264682187</v>
       </c>
       <c r="G111" t="n">
-        <v>1.800635846615244</v>
+        <v>1.795943468710192</v>
       </c>
       <c r="H111" t="n">
-        <v>1.582334459576724</v>
+        <v>1.579780414093636</v>
       </c>
       <c r="I111" t="n">
-        <v>1.347952253454476</v>
+        <v>1.34667211658435</v>
       </c>
       <c r="J111" t="n">
-        <v>1.12301069490283</v>
+        <v>1.122350884722164</v>
       </c>
       <c r="K111" t="n">
-        <v>0.9147720553593836</v>
+        <v>0.9143820207947532</v>
       </c>
       <c r="L111" t="n">
-        <v>0.7510065886977403</v>
+        <v>0.7507417739787408</v>
       </c>
       <c r="M111" t="n">
-        <v>0.6404097196097839</v>
+        <v>0.6402394839972682</v>
       </c>
       <c r="N111" t="n">
-        <v>0.5711549445655631</v>
+        <v>0.5710248710766785</v>
       </c>
       <c r="O111" t="n">
-        <v>0.5175876865192479</v>
+        <v>0.5174221850960193</v>
       </c>
       <c r="P111" t="n">
-        <v>0.4908575613648621</v>
+        <v>0.4905726150255923</v>
       </c>
       <c r="Q111" t="n">
-        <v>0.4736343645899582</v>
+        <v>0.4731421341300526</v>
       </c>
       <c r="R111" t="n">
-        <v>0.452237010736968</v>
+        <v>0.4514995870396917</v>
       </c>
       <c r="S111" t="n">
-        <v>0.4200430095299367</v>
+        <v>0.4190909505129483</v>
       </c>
       <c r="T111" t="n">
-        <v>0.3794184875410938</v>
+        <v>0.3783271950216064</v>
       </c>
       <c r="U111" t="n">
-        <v>0.3376683189063426</v>
+        <v>0.3365311637451408</v>
       </c>
       <c r="V111" t="n">
-        <v>0.2990087275698004</v>
+        <v>0.2978791444982899</v>
       </c>
     </row>
     <row r="112">
@@ -8886,58 +8886,58 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1.741310481107063</v>
+        <v>1.745930373056722</v>
       </c>
       <c r="F112" t="n">
-        <v>1.706679740315541</v>
+        <v>1.714478539207924</v>
       </c>
       <c r="G112" t="n">
-        <v>1.554488953912058</v>
+        <v>1.565536777295986</v>
       </c>
       <c r="H112" t="n">
-        <v>1.361675502636347</v>
+        <v>1.374447417932256</v>
       </c>
       <c r="I112" t="n">
-        <v>1.163496214367836</v>
+        <v>1.176399657498624</v>
       </c>
       <c r="J112" t="n">
-        <v>0.9744452945061178</v>
+        <v>0.9863220231599019</v>
       </c>
       <c r="K112" t="n">
-        <v>0.7986427585016399</v>
+        <v>0.8088468318608142</v>
       </c>
       <c r="L112" t="n">
-        <v>0.6600131148612415</v>
+        <v>0.6686068849064337</v>
       </c>
       <c r="M112" t="n">
-        <v>0.5670541447310498</v>
+        <v>0.5744653370940519</v>
       </c>
       <c r="N112" t="n">
-        <v>0.509346536089171</v>
+        <v>0.5160053735601636</v>
       </c>
       <c r="O112" t="n">
-        <v>0.4644508990084891</v>
+        <v>0.4705099801505093</v>
       </c>
       <c r="P112" t="n">
-        <v>0.4425588090732303</v>
+        <v>0.4483033638766144</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.4283717132500738</v>
+        <v>0.4339067202771069</v>
       </c>
       <c r="R112" t="n">
-        <v>0.4101256296547012</v>
+        <v>0.4153825667685443</v>
       </c>
       <c r="S112" t="n">
-        <v>0.3824264629809416</v>
+        <v>0.3872547677445582</v>
       </c>
       <c r="T112" t="n">
-        <v>0.347293227293304</v>
+        <v>0.351599440209884</v>
       </c>
       <c r="U112" t="n">
-        <v>0.3111978889091562</v>
+        <v>0.3149717890579945</v>
       </c>
       <c r="V112" t="n">
-        <v>0.2777653056827459</v>
+        <v>0.2810449603416105</v>
       </c>
     </row>
     <row r="113">
@@ -8962,19 +8962,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1.655564965995058</v>
+        <v>1.659800937364681</v>
       </c>
       <c r="F113" t="n">
-        <v>1.763783206167686</v>
+        <v>1.767995432947723</v>
       </c>
       <c r="G113" t="n">
-        <v>1.406936927168848</v>
+        <v>1.407688826832949</v>
       </c>
       <c r="H113" t="n">
-        <v>1.151446105671245</v>
+        <v>1.149061099083361</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9729497757511493</v>
+        <v>0.9656349351903827</v>
       </c>
       <c r="J113" t="n">
         <v>1.360411249542888</v>
@@ -9038,19 +9038,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.6726800522688137</v>
+        <v>0.6630494788692494</v>
       </c>
       <c r="F114" t="n">
-        <v>1.053330337411511</v>
+        <v>1.0431977615945</v>
       </c>
       <c r="G114" t="n">
-        <v>1.306623628078382</v>
+        <v>1.300826009145756</v>
       </c>
       <c r="H114" t="n">
-        <v>1.461723573638728</v>
+        <v>1.458756625911462</v>
       </c>
       <c r="I114" t="n">
-        <v>1.466783343775254</v>
+        <v>1.465918102052367</v>
       </c>
       <c r="J114" t="n">
         <v>1.363879708129492</v>
@@ -9114,19 +9114,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1.359206696455503</v>
+        <v>1.359037824504713</v>
       </c>
       <c r="F115" t="n">
-        <v>1.689762628258856</v>
+        <v>1.689607867321872</v>
       </c>
       <c r="G115" t="n">
-        <v>1.703192543820817</v>
+        <v>1.70344712001384</v>
       </c>
       <c r="H115" t="n">
-        <v>1.652030511929305</v>
+        <v>1.652753547040043</v>
       </c>
       <c r="I115" t="n">
-        <v>1.525002271660471</v>
+        <v>1.526642510925306</v>
       </c>
       <c r="J115" t="n">
         <v>1.331382211489245</v>
@@ -9190,58 +9190,58 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.4936859194099285</v>
+        <v>0.4866244995426822</v>
       </c>
       <c r="F116" t="n">
-        <v>0.5451451894439951</v>
+        <v>0.5334935454921993</v>
       </c>
       <c r="G116" t="n">
-        <v>0.5340689755523405</v>
+        <v>0.5211112813510874</v>
       </c>
       <c r="H116" t="n">
-        <v>0.5034697262625126</v>
+        <v>0.4904996734393517</v>
       </c>
       <c r="I116" t="n">
-        <v>0.4596871826427139</v>
+        <v>0.4473089978138304</v>
       </c>
       <c r="J116" t="n">
-        <v>0.4157487025340681</v>
+        <v>0.4040862189283561</v>
       </c>
       <c r="K116" t="n">
-        <v>0.3668850735854415</v>
+        <v>0.3561733257432753</v>
       </c>
       <c r="L116" t="n">
-        <v>0.3194366392868109</v>
+        <v>0.310100705921212</v>
       </c>
       <c r="M116" t="n">
-        <v>0.2819198812239783</v>
+        <v>0.2738459844965611</v>
       </c>
       <c r="N116" t="n">
-        <v>0.2508394271506947</v>
+        <v>0.2437707485037274</v>
       </c>
       <c r="O116" t="n">
-        <v>0.224314936070441</v>
+        <v>0.2180034134254034</v>
       </c>
       <c r="P116" t="n">
-        <v>0.2060356723999512</v>
+        <v>0.2001934937271775</v>
       </c>
       <c r="Q116" t="n">
-        <v>0.190002008326832</v>
+        <v>0.1845389731270421</v>
       </c>
       <c r="R116" t="n">
-        <v>0.1743551310964377</v>
+        <v>0.1692274097647104</v>
       </c>
       <c r="S116" t="n">
-        <v>0.1580626908408926</v>
+        <v>0.153245480320524</v>
       </c>
       <c r="T116" t="n">
-        <v>0.1421038372700333</v>
+        <v>0.1375294077121522</v>
       </c>
       <c r="U116" t="n">
-        <v>0.1286297113177542</v>
+        <v>0.1241434025033553</v>
       </c>
       <c r="V116" t="n">
-        <v>0.1191697618141055</v>
+        <v>0.1145199947169273</v>
       </c>
     </row>
     <row r="117">
@@ -9266,58 +9266,58 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1.726296233365286</v>
+        <v>1.727299953300441</v>
       </c>
       <c r="F117" t="n">
-        <v>2.227147409676222</v>
+        <v>2.231315743694449</v>
       </c>
       <c r="G117" t="n">
-        <v>2.309016007552209</v>
+        <v>2.31480065457561</v>
       </c>
       <c r="H117" t="n">
-        <v>2.224805245415999</v>
+        <v>2.231085121043584</v>
       </c>
       <c r="I117" t="n">
-        <v>2.043045122720488</v>
+        <v>2.049182348788176</v>
       </c>
       <c r="J117" t="n">
-        <v>1.844108010871976</v>
+        <v>1.849871803113676</v>
       </c>
       <c r="K117" t="n">
-        <v>1.61877186431556</v>
+        <v>1.62399113849851</v>
       </c>
       <c r="L117" t="n">
-        <v>1.374317383809961</v>
+        <v>1.378475434757878</v>
       </c>
       <c r="M117" t="n">
-        <v>1.172096175661905</v>
+        <v>1.175252039711076</v>
       </c>
       <c r="N117" t="n">
-        <v>1.011957840552316</v>
+        <v>1.014406194693817</v>
       </c>
       <c r="O117" t="n">
-        <v>0.8863253499710935</v>
+        <v>0.8883324971680817</v>
       </c>
       <c r="P117" t="n">
-        <v>0.801306124738825</v>
+        <v>0.8030471076689246</v>
       </c>
       <c r="Q117" t="n">
-        <v>0.7281476783780355</v>
+        <v>0.7296810513888754</v>
       </c>
       <c r="R117" t="n">
-        <v>0.6581418263381585</v>
+        <v>0.6594964933276019</v>
       </c>
       <c r="S117" t="n">
-        <v>0.5877311880448406</v>
+        <v>0.5889345430731487</v>
       </c>
       <c r="T117" t="n">
-        <v>0.5198857537902385</v>
+        <v>0.5209705573136268</v>
       </c>
       <c r="U117" t="n">
-        <v>0.4611516912738601</v>
+        <v>0.4621606103882913</v>
       </c>
       <c r="V117" t="n">
-        <v>0.4171814596563301</v>
+        <v>0.418187601016649</v>
       </c>
     </row>
     <row r="118">
@@ -9342,58 +9342,58 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1.277543809712957</v>
+        <v>1.27881666411928</v>
       </c>
       <c r="F118" t="n">
-        <v>1.308019446401145</v>
+        <v>1.309728512535076</v>
       </c>
       <c r="G118" t="n">
-        <v>1.197057900897149</v>
+        <v>1.198444652224864</v>
       </c>
       <c r="H118" t="n">
-        <v>1.070930497858531</v>
+        <v>1.071883129915818</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9403803896715655</v>
+        <v>0.9409599081217292</v>
       </c>
       <c r="J118" t="n">
-        <v>0.8235781046397272</v>
+        <v>0.8238567918184849</v>
       </c>
       <c r="K118" t="n">
-        <v>0.7063706299965611</v>
+        <v>0.7064068299980983</v>
       </c>
       <c r="L118" t="n">
-        <v>0.58881609598198</v>
+        <v>0.5885051633054879</v>
       </c>
       <c r="M118" t="n">
-        <v>0.495537977563987</v>
+        <v>0.4949397219187436</v>
       </c>
       <c r="N118" t="n">
-        <v>0.4243728657866885</v>
+        <v>0.4236222883426191</v>
       </c>
       <c r="O118" t="n">
-        <v>0.3702131969996936</v>
+        <v>0.3694173867116426</v>
       </c>
       <c r="P118" t="n">
-        <v>0.3342266724675455</v>
+        <v>0.3334130906815474</v>
       </c>
       <c r="Q118" t="n">
-        <v>0.3037361860742155</v>
+        <v>0.3029168936733963</v>
       </c>
       <c r="R118" t="n">
-        <v>0.2753032715156472</v>
+        <v>0.2744919472741394</v>
       </c>
       <c r="S118" t="n">
-        <v>0.2466709532082344</v>
+        <v>0.2458758935018995</v>
       </c>
       <c r="T118" t="n">
-        <v>0.2188889387570919</v>
+        <v>0.2181064718605908</v>
       </c>
       <c r="U118" t="n">
-        <v>0.1953431523247906</v>
+        <v>0.1945568877337134</v>
       </c>
       <c r="V118" t="n">
-        <v>0.1779058143081696</v>
+        <v>0.1770809954399242</v>
       </c>
     </row>
     <row r="119">
@@ -9418,58 +9418,58 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1.183062842718331</v>
+        <v>1.182448993847636</v>
       </c>
       <c r="F119" t="n">
-        <v>1.431762088832406</v>
+        <v>1.43208594320935</v>
       </c>
       <c r="G119" t="n">
-        <v>1.520065350088427</v>
+        <v>1.521621682125827</v>
       </c>
       <c r="H119" t="n">
-        <v>1.516926025052926</v>
+        <v>1.519311226832782</v>
       </c>
       <c r="I119" t="n">
-        <v>1.431521482865064</v>
+        <v>1.434249219145511</v>
       </c>
       <c r="J119" t="n">
-        <v>1.313569748859637</v>
+        <v>1.31632165565436</v>
       </c>
       <c r="K119" t="n">
-        <v>1.16106967328737</v>
+        <v>1.163618185687745</v>
       </c>
       <c r="L119" t="n">
-        <v>0.9862673117664568</v>
+        <v>0.9881892326637661</v>
       </c>
       <c r="M119" t="n">
-        <v>0.8406001889146946</v>
+        <v>0.8419106214789438</v>
       </c>
       <c r="N119" t="n">
-        <v>0.7265649936163422</v>
+        <v>0.727469042886574</v>
       </c>
       <c r="O119" t="n">
-        <v>0.638779748850958</v>
+        <v>0.6394662253559541</v>
       </c>
       <c r="P119" t="n">
-        <v>0.5798944200819857</v>
+        <v>0.5804583246230924</v>
       </c>
       <c r="Q119" t="n">
-        <v>0.5287320160089297</v>
+        <v>0.529200030778911</v>
       </c>
       <c r="R119" t="n">
-        <v>0.4792582908608885</v>
+        <v>0.4796420871632795</v>
       </c>
       <c r="S119" t="n">
-        <v>0.4283810704559664</v>
+        <v>0.4286894278962817</v>
       </c>
       <c r="T119" t="n">
-        <v>0.3795323590674036</v>
+        <v>0.3797841218263207</v>
       </c>
       <c r="U119" t="n">
-        <v>0.3379847549433155</v>
+        <v>0.3382017749133262</v>
       </c>
       <c r="V119" t="n">
-        <v>0.3060205734251493</v>
+        <v>0.3062146140097302</v>
       </c>
     </row>
     <row r="120">
@@ -9494,58 +9494,58 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.01165546689831777</v>
+        <v>0.008441620328634169</v>
       </c>
       <c r="F120" t="n">
-        <v>0.01931448987840511</v>
+        <v>0.01401071861626798</v>
       </c>
       <c r="G120" t="n">
-        <v>0.02153697190358303</v>
+        <v>0.01563270772976003</v>
       </c>
       <c r="H120" t="n">
-        <v>0.02158669487862035</v>
+        <v>0.01567431877990884</v>
       </c>
       <c r="I120" t="n">
-        <v>0.0206068451114752</v>
+        <v>0.01496594944767801</v>
       </c>
       <c r="J120" t="n">
-        <v>0.01940860142309699</v>
+        <v>0.014098672668149</v>
       </c>
       <c r="K120" t="n">
-        <v>0.01781352908375755</v>
+        <v>0.01294381644189336</v>
       </c>
       <c r="L120" t="n">
-        <v>0.01549234360171339</v>
+        <v>0.0112556372486153</v>
       </c>
       <c r="M120" t="n">
-        <v>0.01336554851207537</v>
+        <v>0.009708649288919367</v>
       </c>
       <c r="N120" t="n">
-        <v>0.01168137671939927</v>
+        <v>0.008484497906952057</v>
       </c>
       <c r="O120" t="n">
-        <v>0.01042001369899515</v>
+        <v>0.00756736253591284</v>
       </c>
       <c r="P120" t="n">
-        <v>0.009640285688106135</v>
+        <v>0.007000741065816612</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.009011670852415422</v>
+        <v>0.006545039265255851</v>
       </c>
       <c r="R120" t="n">
-        <v>0.008456163016031476</v>
+        <v>0.006141771994486914</v>
       </c>
       <c r="S120" t="n">
-        <v>0.007943184068574459</v>
+        <v>0.005772071314240864</v>
       </c>
       <c r="T120" t="n">
-        <v>0.007545626738368123</v>
+        <v>0.005483695505414258</v>
       </c>
       <c r="U120" t="n">
-        <v>0.007406398517482114</v>
+        <v>0.00538609644208089</v>
       </c>
       <c r="V120" t="n">
-        <v>0.007688218397223129</v>
+        <v>0.00559528968188377</v>
       </c>
     </row>
     <row r="121">
@@ -9570,58 +9570,58 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.01226943943244362</v>
+        <v>0.008887106540876023</v>
       </c>
       <c r="F121" t="n">
-        <v>0.01800877338078153</v>
+        <v>0.01306319606439721</v>
       </c>
       <c r="G121" t="n">
-        <v>0.01828772005960531</v>
+        <v>0.0132742318424621</v>
       </c>
       <c r="H121" t="n">
-        <v>0.01737281924995608</v>
+        <v>0.01261448840277049</v>
       </c>
       <c r="I121" t="n">
-        <v>0.01627343096716912</v>
+        <v>0.01181904334734798</v>
       </c>
       <c r="J121" t="n">
-        <v>0.01539926403059673</v>
+        <v>0.0111865922837749</v>
       </c>
       <c r="K121" t="n">
-        <v>0.01438443476903629</v>
+        <v>0.0104515120411348</v>
       </c>
       <c r="L121" t="n">
-        <v>0.01305678682122307</v>
+        <v>0.009486279584870449</v>
       </c>
       <c r="M121" t="n">
-        <v>0.01183223780590507</v>
+        <v>0.008594776887720038</v>
       </c>
       <c r="N121" t="n">
-        <v>0.01074886224049339</v>
+        <v>0.007806692433248944</v>
       </c>
       <c r="O121" t="n">
-        <v>0.009809218810772439</v>
+        <v>0.007123892490699752</v>
       </c>
       <c r="P121" t="n">
-        <v>0.009204843147122183</v>
+        <v>0.006685188441256016</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.008700351511847573</v>
+        <v>0.006319165679606338</v>
       </c>
       <c r="R121" t="n">
-        <v>0.008243443539723165</v>
+        <v>0.005988002688164884</v>
       </c>
       <c r="S121" t="n">
-        <v>0.007813912840845195</v>
+        <v>0.005677155285685553</v>
       </c>
       <c r="T121" t="n">
-        <v>0.007471174059839042</v>
+        <v>0.005430106385237722</v>
       </c>
       <c r="U121" t="n">
-        <v>0.007360081468864224</v>
+        <v>0.005352304344399926</v>
       </c>
       <c r="V121" t="n">
-        <v>0.00766609504675842</v>
+        <v>0.005579875883205085</v>
       </c>
     </row>
     <row r="122">
@@ -9646,58 +9646,58 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1.489899031284905</v>
+        <v>1.490549873691243</v>
       </c>
       <c r="F122" t="n">
-        <v>1.562538456854272</v>
+        <v>1.563361271275784</v>
       </c>
       <c r="G122" t="n">
-        <v>1.491936319482445</v>
+        <v>1.49271116822228</v>
       </c>
       <c r="H122" t="n">
-        <v>1.388546283864124</v>
+        <v>1.389253588625652</v>
       </c>
       <c r="I122" t="n">
-        <v>1.260750248087751</v>
+        <v>1.261400991047425</v>
       </c>
       <c r="J122" t="n">
-        <v>1.13852669979001</v>
+        <v>1.13914098871813</v>
       </c>
       <c r="K122" t="n">
-        <v>1.004971634978885</v>
+        <v>1.005548663621463</v>
       </c>
       <c r="L122" t="n">
-        <v>0.8851593389578356</v>
+        <v>0.8857109591934512</v>
       </c>
       <c r="M122" t="n">
-        <v>0.7932478638788071</v>
+        <v>0.7937772832833854</v>
       </c>
       <c r="N122" t="n">
-        <v>0.7139735503337108</v>
+        <v>0.7144731351520331</v>
       </c>
       <c r="O122" t="n">
-        <v>0.6421591661346262</v>
+        <v>0.6426225792060725</v>
       </c>
       <c r="P122" t="n">
-        <v>0.5913592469774442</v>
+        <v>0.59179660488078</v>
       </c>
       <c r="Q122" t="n">
-        <v>0.5459304992841411</v>
+        <v>0.546344364582855</v>
       </c>
       <c r="R122" t="n">
-        <v>0.5007534965138535</v>
+        <v>0.5011440700995037</v>
       </c>
       <c r="S122" t="n">
-        <v>0.4528133436400782</v>
+        <v>0.4531799341984095</v>
       </c>
       <c r="T122" t="n">
-        <v>0.404742714438872</v>
+        <v>0.405087567200831</v>
       </c>
       <c r="U122" t="n">
-        <v>0.3624609889387311</v>
+        <v>0.362792977632403</v>
       </c>
       <c r="V122" t="n">
-        <v>0.3299274681225133</v>
+        <v>0.3302636482951026</v>
       </c>
     </row>
     <row r="123">
@@ -9725,10 +9725,10 @@
         <v>2.381334136564795</v>
       </c>
       <c r="F123" t="n">
-        <v>2.098569342276071</v>
+        <v>2.098572046733016</v>
       </c>
       <c r="G123" t="n">
-        <v>1.678137451337412</v>
+        <v>1.67813999080712</v>
       </c>
       <c r="H123" t="n">
         <v>1.3255914401649</v>
@@ -9798,19 +9798,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1.042786594950945</v>
+        <v>1.042791827694664</v>
       </c>
       <c r="F124" t="n">
-        <v>0.9098783230430693</v>
+        <v>0.9098810764137457</v>
       </c>
       <c r="G124" t="n">
-        <v>0.7604079570246716</v>
+        <v>0.7604098683675533</v>
       </c>
       <c r="H124" t="n">
-        <v>0.6377429571485335</v>
+        <v>0.6377441112413588</v>
       </c>
       <c r="I124" t="n">
-        <v>0.51514476306944</v>
+        <v>0.5151452341449336</v>
       </c>
       <c r="J124" t="n">
         <v>0.3938620618151116</v>
@@ -9874,19 +9874,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2.124920117534388</v>
+        <v>2.124916703483622</v>
       </c>
       <c r="F125" t="n">
-        <v>2.152475106496666</v>
+        <v>2.152473261440089</v>
       </c>
       <c r="G125" t="n">
-        <v>2.143885605115036</v>
+        <v>2.14388429001143</v>
       </c>
       <c r="H125" t="n">
-        <v>2.020966442665764</v>
+        <v>2.020965628511766</v>
       </c>
       <c r="I125" t="n">
-        <v>1.736519744804771</v>
+        <v>1.736519404762094</v>
       </c>
       <c r="J125" t="n">
         <v>1.356289185310689</v>
@@ -10254,19 +10254,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.3424213334167794</v>
+        <v>0.5444575537974703</v>
       </c>
       <c r="F130" t="n">
-        <v>0.3143732800170982</v>
+        <v>0.4766625778302253</v>
       </c>
       <c r="G130" t="n">
-        <v>0.309984167648759</v>
+        <v>0.4541361913947978</v>
       </c>
       <c r="H130" t="n">
-        <v>0.2620425491508395</v>
+        <v>0.3711893454059261</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1881953621546787</v>
+        <v>0.2478092230593646</v>
       </c>
       <c r="J130" t="n">
         <v>0.102271011775041</v>
@@ -10330,19 +10330,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.4756142535591486</v>
+        <v>0.665952644667823</v>
       </c>
       <c r="F131" t="n">
-        <v>0.4893489677774643</v>
+        <v>0.6548607809163074</v>
       </c>
       <c r="G131" t="n">
-        <v>0.5294848054928937</v>
+        <v>0.6711013546052104</v>
       </c>
       <c r="H131" t="n">
-        <v>0.5044566719393901</v>
+        <v>0.6058192623829699</v>
       </c>
       <c r="I131" t="n">
-        <v>0.4402276694938874</v>
+        <v>0.4931065794076328</v>
       </c>
       <c r="J131" t="n">
         <v>0.3527059878738122</v>
@@ -10406,19 +10406,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1.02539043710885</v>
+        <v>1.070254879446555</v>
       </c>
       <c r="F132" t="n">
-        <v>1.449048947165207</v>
+        <v>1.470958448007059</v>
       </c>
       <c r="G132" t="n">
-        <v>1.924344757643051</v>
+        <v>1.927313365976493</v>
       </c>
       <c r="H132" t="n">
-        <v>2.152846235039183</v>
+        <v>2.146342665264948</v>
       </c>
       <c r="I132" t="n">
-        <v>2.14455100719076</v>
+        <v>2.138797058133047</v>
       </c>
       <c r="J132" t="n">
         <v>1.954474447118985</v>
@@ -10482,19 +10482,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2.763657029484965</v>
+        <v>2.70453738699931</v>
       </c>
       <c r="F133" t="n">
-        <v>2.192574751074157</v>
+        <v>2.172827628682689</v>
       </c>
       <c r="G133" t="n">
-        <v>1.734773150960802</v>
+        <v>1.739049796683335</v>
       </c>
       <c r="H133" t="n">
-        <v>1.424511659210579</v>
+        <v>1.437324838992364</v>
       </c>
       <c r="I133" t="n">
-        <v>1.274426948200406</v>
+        <v>1.282566502122725</v>
       </c>
       <c r="J133" t="n">
         <v>1.187261175878712</v>
@@ -10558,19 +10558,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.3655850034092671</v>
+        <v>0.4350444755746548</v>
       </c>
       <c r="F134" t="n">
-        <v>0.5650352266783262</v>
+        <v>0.6050435897763836</v>
       </c>
       <c r="G134" t="n">
-        <v>0.8561187544542298</v>
+        <v>0.8762698379795514</v>
       </c>
       <c r="H134" t="n">
-        <v>1.050135274489762</v>
+        <v>1.056837052966108</v>
       </c>
       <c r="I134" t="n">
-        <v>1.12586228297206</v>
+        <v>1.1266050967914</v>
       </c>
       <c r="J134" t="n">
         <v>1.114695504835602</v>
@@ -10634,19 +10634,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3.473891721508846</v>
+        <v>3.387487732029766</v>
       </c>
       <c r="F135" t="n">
-        <v>3.839267982681344</v>
+        <v>3.762412218451331</v>
       </c>
       <c r="G135" t="n">
-        <v>3.769033168048141</v>
+        <v>3.704569983855597</v>
       </c>
       <c r="H135" t="n">
-        <v>3.357388696209396</v>
+        <v>3.316188477939355</v>
       </c>
       <c r="I135" t="n">
-        <v>2.953637469909505</v>
+        <v>2.934182409148101</v>
       </c>
       <c r="J135" t="n">
         <v>2.607614549160278</v>
@@ -10710,19 +10710,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.4799189612431166</v>
+        <v>0.7641308410093008</v>
       </c>
       <c r="F136" t="n">
-        <v>0.4369897353337605</v>
+        <v>0.6304163841570191</v>
       </c>
       <c r="G136" t="n">
-        <v>0.5071851689618755</v>
+        <v>0.6378348629311755</v>
       </c>
       <c r="H136" t="n">
-        <v>0.6035375984433832</v>
+        <v>0.6769084394048807</v>
       </c>
       <c r="I136" t="n">
-        <v>0.6663850834744526</v>
+        <v>0.698181920655143</v>
       </c>
       <c r="J136" t="n">
         <v>0.6614049755072261</v>
@@ -10786,19 +10786,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.657179975060052</v>
+        <v>0.6958195178185272</v>
       </c>
       <c r="F137" t="n">
-        <v>0.8611118642500833</v>
+        <v>0.8869325548493829</v>
       </c>
       <c r="G137" t="n">
-        <v>1.135188442011715</v>
+        <v>1.147869850690987</v>
       </c>
       <c r="H137" t="n">
-        <v>1.270322571251899</v>
+        <v>1.274094352776336</v>
       </c>
       <c r="I137" t="n">
-        <v>1.278572601271764</v>
+        <v>1.278865958169809</v>
       </c>
       <c r="J137" t="n">
         <v>1.200898458770331</v>
@@ -10862,19 +10862,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.6532150086962419</v>
+        <v>0.8930340847250667</v>
       </c>
       <c r="F138" t="n">
-        <v>0.7518607658222465</v>
+        <v>0.929394929072741</v>
       </c>
       <c r="G138" t="n">
-        <v>0.9185088598842972</v>
+        <v>1.056013575640733</v>
       </c>
       <c r="H138" t="n">
-        <v>1.012012108475388</v>
+        <v>1.100222133901009</v>
       </c>
       <c r="I138" t="n">
-        <v>1.060139463038648</v>
+        <v>1.100684811969753</v>
       </c>
       <c r="J138" t="n">
         <v>1.069463972840413</v>
@@ -10938,19 +10938,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1.616076056818221</v>
+        <v>2.058366789241693</v>
       </c>
       <c r="F139" t="n">
-        <v>1.906896673869151</v>
+        <v>2.251556405684846</v>
       </c>
       <c r="G139" t="n">
-        <v>2.152918757414458</v>
+        <v>2.451759842750223</v>
       </c>
       <c r="H139" t="n">
-        <v>2.055762015605424</v>
+        <v>2.28078141322128</v>
       </c>
       <c r="I139" t="n">
-        <v>1.806698114871624</v>
+        <v>1.929582983698843</v>
       </c>
       <c r="J139" t="n">
         <v>1.507123450310498</v>
@@ -11014,19 +11014,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.5928331019973392</v>
+        <v>0.770984255674417</v>
       </c>
       <c r="F140" t="n">
-        <v>0.8096964595456886</v>
+        <v>0.9228741153970154</v>
       </c>
       <c r="G140" t="n">
-        <v>1.148966820552509</v>
+        <v>1.223002331395891</v>
       </c>
       <c r="H140" t="n">
-        <v>1.341122182839564</v>
+        <v>1.383679479653532</v>
       </c>
       <c r="I140" t="n">
-        <v>1.367962586097123</v>
+        <v>1.387338403658043</v>
       </c>
       <c r="J140" t="n">
         <v>1.282597165871206</v>
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4.886996336830598</v>
+        <v>4.725366135953537</v>
       </c>
       <c r="F141" t="n">
-        <v>6.070133475121639</v>
+        <v>5.904912542779136</v>
       </c>
       <c r="G141" t="n">
-        <v>6.730218079545169</v>
+        <v>6.563603774311634</v>
       </c>
       <c r="H141" t="n">
-        <v>6.472913319558059</v>
+        <v>6.347697925217244</v>
       </c>
       <c r="I141" t="n">
-        <v>5.849762255087286</v>
+        <v>5.784654518274865</v>
       </c>
       <c r="J141" t="n">
         <v>5.093938458952206</v>
@@ -11166,19 +11166,19 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>8.710574760783535</v>
+        <v>8.406885912649171</v>
       </c>
       <c r="F142" t="n">
-        <v>5.873725172626417</v>
+        <v>5.710415768451184</v>
       </c>
       <c r="G142" t="n">
-        <v>3.196285978542792</v>
+        <v>3.121551390911458</v>
       </c>
       <c r="H142" t="n">
-        <v>1.897189209192448</v>
+        <v>1.867371466576375</v>
       </c>
       <c r="I142" t="n">
-        <v>1.36003077777353</v>
+        <v>1.349647927360856</v>
       </c>
       <c r="J142" t="n">
         <v>1.156255584852159</v>
@@ -11470,19 +11470,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2.816639345558431</v>
+        <v>2.317747563501811</v>
       </c>
       <c r="F146" t="n">
-        <v>4.325671437808799</v>
+        <v>3.582628460804978</v>
       </c>
       <c r="G146" t="n">
-        <v>5.178758202635377</v>
+        <v>4.292253446950148</v>
       </c>
       <c r="H146" t="n">
-        <v>5.298713301582128</v>
+        <v>4.490235569718647</v>
       </c>
       <c r="I146" t="n">
-        <v>5.052335165584965</v>
+        <v>4.52867510193833</v>
       </c>
       <c r="J146" t="n">
         <v>4.898316991237228</v>
@@ -11546,19 +11546,19 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1.171294242718625</v>
+        <v>1.214841358579101</v>
       </c>
       <c r="F147" t="n">
-        <v>1.354847070101006</v>
+        <v>1.392084568547743</v>
       </c>
       <c r="G147" t="n">
-        <v>1.389174534916332</v>
+        <v>1.399828266145925</v>
       </c>
       <c r="H147" t="n">
-        <v>1.32008492771277</v>
+        <v>1.311015423770913</v>
       </c>
       <c r="I147" t="n">
-        <v>1.187259420626036</v>
+        <v>1.179325554109978</v>
       </c>
       <c r="J147" t="n">
         <v>1.049738399247365</v>
@@ -11622,19 +11622,19 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1.490754555697395</v>
+        <v>1.502213512358809</v>
       </c>
       <c r="F148" t="n">
-        <v>1.733148511676747</v>
+        <v>1.749840012287448</v>
       </c>
       <c r="G148" t="n">
-        <v>1.726936257871273</v>
+        <v>1.746466266263981</v>
       </c>
       <c r="H148" t="n">
-        <v>1.583963786267862</v>
+        <v>1.601225205454051</v>
       </c>
       <c r="I148" t="n">
-        <v>1.397913274141675</v>
+        <v>1.40859130267462</v>
       </c>
       <c r="J148" t="n">
         <v>1.219011017842645</v>
@@ -11698,19 +11698,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.5962605320278814</v>
+        <v>0.5807362779271055</v>
       </c>
       <c r="F149" t="n">
-        <v>0.6664771721419566</v>
+        <v>0.6366416295445267</v>
       </c>
       <c r="G149" t="n">
-        <v>0.7055745688115185</v>
+        <v>0.6638773539227046</v>
       </c>
       <c r="H149" t="n">
-        <v>0.7277916062550907</v>
+        <v>0.6775195429336199</v>
       </c>
       <c r="I149" t="n">
-        <v>0.7273940305745409</v>
+        <v>0.673017260141792</v>
       </c>
       <c r="J149" t="n">
         <v>0.9023915219993891</v>
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1.306816670821906</v>
+        <v>1.325809822537571</v>
       </c>
       <c r="F150" t="n">
-        <v>1.296347612463032</v>
+        <v>1.32801479660111</v>
       </c>
       <c r="G150" t="n">
-        <v>1.229756697968062</v>
+        <v>1.270946628468354</v>
       </c>
       <c r="H150" t="n">
-        <v>1.103953721940339</v>
+        <v>1.153784027025969</v>
       </c>
       <c r="I150" t="n">
-        <v>0.8621237537601397</v>
+        <v>0.9204091713343671</v>
       </c>
       <c r="J150" t="n">
         <v>0.3384169447778125</v>
@@ -11850,19 +11850,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.7938113322668836</v>
+        <v>0.7945075883504057</v>
       </c>
       <c r="F151" t="n">
-        <v>0.8597314718831026</v>
+        <v>0.8622380160440702</v>
       </c>
       <c r="G151" t="n">
-        <v>0.8760533350552848</v>
+        <v>0.8817999295674015</v>
       </c>
       <c r="H151" t="n">
-        <v>0.8360119774867825</v>
+        <v>0.8447991437687293</v>
       </c>
       <c r="I151" t="n">
-        <v>0.7155476845418711</v>
+        <v>0.7262080367524034</v>
       </c>
       <c r="J151" t="n">
         <v>0.5202986830619758</v>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.5299363399162241</v>
+        <v>0.5285645472699975</v>
       </c>
       <c r="F152" t="n">
-        <v>0.5911018098232791</v>
+        <v>0.59069442202522</v>
       </c>
       <c r="G152" t="n">
-        <v>0.5943687010469568</v>
+        <v>0.5941025476541918</v>
       </c>
       <c r="H152" t="n">
-        <v>0.5619125348375466</v>
+        <v>0.5604966008384326</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4916406220522946</v>
+        <v>0.4878918011344342</v>
       </c>
       <c r="J152" t="n">
         <v>0.4455727119923735</v>
@@ -12002,19 +12002,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.3502524366325467</v>
+        <v>0.3276963418477427</v>
       </c>
       <c r="F153" t="n">
-        <v>0.4300602069816484</v>
+        <v>0.3879939435266918</v>
       </c>
       <c r="G153" t="n">
-        <v>0.4885652842896939</v>
+        <v>0.4333545056121662</v>
       </c>
       <c r="H153" t="n">
-        <v>0.5321517917971795</v>
+        <v>0.4680989776744021</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5735413233443363</v>
+        <v>0.502526896752821</v>
       </c>
       <c r="J153" t="n">
         <v>0.8956174008445273</v>
@@ -12078,19 +12078,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.5744784258641753</v>
+        <v>0.57821162778345</v>
       </c>
       <c r="F154" t="n">
-        <v>0.6322787772919581</v>
+        <v>0.6409742704372406</v>
       </c>
       <c r="G154" t="n">
-        <v>0.6256774218776384</v>
+        <v>0.6379627012862055</v>
       </c>
       <c r="H154" t="n">
-        <v>0.5708582506112594</v>
+        <v>0.584792692034703</v>
       </c>
       <c r="I154" t="n">
-        <v>0.4640291833643435</v>
+        <v>0.4778303414064726</v>
       </c>
       <c r="J154" t="n">
         <v>0.31038449304273</v>
@@ -12154,58 +12154,58 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.069614929524955</v>
+        <v>0.06961459008385044</v>
       </c>
       <c r="F155" t="n">
-        <v>0.08079125026242637</v>
+        <v>0.08079054202742388</v>
       </c>
       <c r="G155" t="n">
-        <v>0.07958876846691205</v>
+        <v>0.07958785354148191</v>
       </c>
       <c r="H155" t="n">
-        <v>0.07989527251736316</v>
+        <v>0.07989422373228627</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0782034569566212</v>
+        <v>0.07820236935032225</v>
       </c>
       <c r="J155" t="n">
-        <v>0.07693654795293631</v>
+        <v>0.07693549343087298</v>
       </c>
       <c r="K155" t="n">
-        <v>0.07687725575518332</v>
+        <v>0.07687623994976756</v>
       </c>
       <c r="L155" t="n">
-        <v>0.07748928799794329</v>
+        <v>0.0774883156777566</v>
       </c>
       <c r="M155" t="n">
-        <v>0.07985187815972998</v>
+        <v>0.07985093935036938</v>
       </c>
       <c r="N155" t="n">
-        <v>0.0804786172796669</v>
+        <v>0.08047774982650938</v>
       </c>
       <c r="O155" t="n">
-        <v>0.07813010778913954</v>
+        <v>0.07812933422641907</v>
       </c>
       <c r="P155" t="n">
-        <v>0.07415556511298943</v>
+        <v>0.07415487793382554</v>
       </c>
       <c r="Q155" t="n">
-        <v>0.07093398617825249</v>
+        <v>0.0709333645903262</v>
       </c>
       <c r="R155" t="n">
-        <v>0.0682533045392547</v>
+        <v>0.06825271477864885</v>
       </c>
       <c r="S155" t="n">
-        <v>0.064814791842772</v>
+        <v>0.06481424543632475</v>
       </c>
       <c r="T155" t="n">
-        <v>0.06001793322483004</v>
+        <v>0.06001741286098568</v>
       </c>
       <c r="U155" t="n">
-        <v>0.05458570346101698</v>
+        <v>0.0545852220768208</v>
       </c>
       <c r="V155" t="n">
-        <v>0.04958117025149364</v>
+        <v>0.04958072667313169</v>
       </c>
     </row>
     <row r="156">
@@ -12230,58 +12230,58 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.1611593899691811</v>
+        <v>0.1611594475506445</v>
       </c>
       <c r="F156" t="n">
-        <v>0.1935024305534324</v>
+        <v>0.1935025834184282</v>
       </c>
       <c r="G156" t="n">
-        <v>0.196289516773811</v>
+        <v>0.1962897704978006</v>
       </c>
       <c r="H156" t="n">
-        <v>0.2006140529531568</v>
+        <v>0.2006143923964698</v>
       </c>
       <c r="I156" t="n">
-        <v>0.1976283992271534</v>
+        <v>0.1976287837279272</v>
       </c>
       <c r="J156" t="n">
-        <v>0.1943524681351159</v>
+        <v>0.1943528602493623</v>
       </c>
       <c r="K156" t="n">
-        <v>0.1930775529288588</v>
+        <v>0.1930779388422375</v>
       </c>
       <c r="L156" t="n">
-        <v>0.1932761035011037</v>
+        <v>0.1932764749650205</v>
       </c>
       <c r="M156" t="n">
-        <v>0.1980350505846516</v>
+        <v>0.1980354155285928</v>
       </c>
       <c r="N156" t="n">
-        <v>0.2003910188396234</v>
+        <v>0.2003913792953091</v>
       </c>
       <c r="O156" t="n">
-        <v>0.1965113736890546</v>
+        <v>0.1965117192037673</v>
       </c>
       <c r="P156" t="n">
-        <v>0.1886226302027588</v>
+        <v>0.1886229675513582</v>
       </c>
       <c r="Q156" t="n">
-        <v>0.1818923695054335</v>
+        <v>0.1818926931164759</v>
       </c>
       <c r="R156" t="n">
-        <v>0.1758277197920692</v>
+        <v>0.175828042952659</v>
       </c>
       <c r="S156" t="n">
-        <v>0.1673263183405822</v>
+        <v>0.1673266350549052</v>
       </c>
       <c r="T156" t="n">
-        <v>0.1550697554894506</v>
+        <v>0.1550700586643414</v>
       </c>
       <c r="U156" t="n">
-        <v>0.141110980277162</v>
+        <v>0.14111126895594</v>
       </c>
       <c r="V156" t="n">
-        <v>0.1281871339400444</v>
+        <v>0.1281874066552126</v>
       </c>
     </row>
     <row r="157">
@@ -12306,58 +12306,58 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.4859188110032224</v>
+        <v>0.4859200741733499</v>
       </c>
       <c r="F157" t="n">
-        <v>0.6945501137023277</v>
+        <v>0.6945536176261383</v>
       </c>
       <c r="G157" t="n">
-        <v>0.7692850664889258</v>
+        <v>0.7692905298353347</v>
       </c>
       <c r="H157" t="n">
-        <v>0.7858323538624234</v>
+        <v>0.7858395900591197</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7359773170159817</v>
+        <v>0.7359842133366961</v>
       </c>
       <c r="J157" t="n">
-        <v>0.6792229983706871</v>
+        <v>0.679228672124187</v>
       </c>
       <c r="K157" t="n">
-        <v>0.6367402102429426</v>
+        <v>0.6367456967497933</v>
       </c>
       <c r="L157" t="n">
-        <v>0.6049777684279586</v>
+        <v>0.6049831168414409</v>
       </c>
       <c r="M157" t="n">
-        <v>0.5901865427251489</v>
+        <v>0.5901909208401778</v>
       </c>
       <c r="N157" t="n">
-        <v>0.5562899962305515</v>
+        <v>0.5562943289298666</v>
       </c>
       <c r="O157" t="n">
-        <v>0.5036131236888206</v>
+        <v>0.5036157190129117</v>
       </c>
       <c r="P157" t="n">
-        <v>0.4504909869569612</v>
+        <v>0.4504936004432473</v>
       </c>
       <c r="Q157" t="n">
-        <v>0.4143994847025493</v>
+        <v>0.4144021390506813</v>
       </c>
       <c r="R157" t="n">
-        <v>0.3906836529124454</v>
+        <v>0.3906863704219024</v>
       </c>
       <c r="S157" t="n">
-        <v>0.3681243924326878</v>
+        <v>0.3681271938957986</v>
       </c>
       <c r="T157" t="n">
-        <v>0.3404850710138697</v>
+        <v>0.3404860392967942</v>
       </c>
       <c r="U157" t="n">
-        <v>0.3101735595805837</v>
+        <v>0.3101755773633028</v>
       </c>
       <c r="V157" t="n">
-        <v>0.2831132332214036</v>
+        <v>0.2831153510959471</v>
       </c>
     </row>
     <row r="158">
@@ -12382,58 +12382,58 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.26905948674021</v>
+        <v>0.2690599960643137</v>
       </c>
       <c r="F158" t="n">
-        <v>0.2827950850214857</v>
+        <v>0.2827959452649708</v>
       </c>
       <c r="G158" t="n">
-        <v>0.251096179654648</v>
+        <v>0.2510970296143867</v>
       </c>
       <c r="H158" t="n">
-        <v>0.2330810549048303</v>
+        <v>0.2330818115620788</v>
       </c>
       <c r="I158" t="n">
-        <v>0.2175966044861036</v>
+        <v>0.2175973156629591</v>
       </c>
       <c r="J158" t="n">
-        <v>0.2087029401830972</v>
+        <v>0.20870360943068</v>
       </c>
       <c r="K158" t="n">
-        <v>0.2070804905416668</v>
+        <v>0.2070811219390756</v>
       </c>
       <c r="L158" t="n">
-        <v>0.2080958987500769</v>
+        <v>0.2080965414784773</v>
       </c>
       <c r="M158" t="n">
-        <v>0.2136166729938695</v>
+        <v>0.2136172837882029</v>
       </c>
       <c r="N158" t="n">
-        <v>0.2102945330528211</v>
+        <v>0.2102950642041205</v>
       </c>
       <c r="O158" t="n">
-        <v>0.1967142993596351</v>
+        <v>0.1967147470976626</v>
       </c>
       <c r="P158" t="n">
-        <v>0.1790066681877699</v>
+        <v>0.1790069765195102</v>
       </c>
       <c r="Q158" t="n">
-        <v>0.1650362794252994</v>
+        <v>0.1650365455791054</v>
       </c>
       <c r="R158" t="n">
-        <v>0.1542796040409759</v>
+        <v>0.1542798251977141</v>
       </c>
       <c r="S158" t="n">
-        <v>0.1432941693733843</v>
+        <v>0.143294284471229</v>
       </c>
       <c r="T158" t="n">
-        <v>0.1306123395598789</v>
+        <v>0.1306125202780892</v>
       </c>
       <c r="U158" t="n">
-        <v>0.1173308108306945</v>
+        <v>0.1173309376746086</v>
       </c>
       <c r="V158" t="n">
-        <v>0.1056816670361339</v>
+        <v>0.1056818013878533</v>
       </c>
     </row>
     <row r="159">
@@ -12458,55 +12458,55 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1.38813168441272</v>
+        <v>1.388137612938415</v>
       </c>
       <c r="F159" t="n">
-        <v>1.542612199504285</v>
+        <v>1.542620582506909</v>
       </c>
       <c r="G159" t="n">
-        <v>1.466323728032436</v>
+        <v>1.466334383815996</v>
       </c>
       <c r="H159" t="n">
-        <v>1.407140966230508</v>
+        <v>1.407153817091131</v>
       </c>
       <c r="I159" t="n">
-        <v>1.306948306835871</v>
+        <v>1.306963298328199</v>
       </c>
       <c r="J159" t="n">
-        <v>1.205641005602419</v>
+        <v>1.205653216628487</v>
       </c>
       <c r="K159" t="n">
-        <v>1.138290957843563</v>
+        <v>1.138302949775391</v>
       </c>
       <c r="L159" t="n">
-        <v>1.084449224107505</v>
+        <v>1.084458699210487</v>
       </c>
       <c r="M159" t="n">
-        <v>1.08080327714474</v>
+        <v>1.080812694227328</v>
       </c>
       <c r="N159" t="n">
-        <v>1.051305844918993</v>
+        <v>1.051315265749863</v>
       </c>
       <c r="O159" t="n">
-        <v>0.9815637473362475</v>
+        <v>0.9815708664967561</v>
       </c>
       <c r="P159" t="n">
-        <v>0.8898626237773033</v>
+        <v>0.8898674482276175</v>
       </c>
       <c r="Q159" t="n">
-        <v>0.8123075475994811</v>
+        <v>0.8123124981435459</v>
       </c>
       <c r="R159" t="n">
-        <v>0.7481576277558336</v>
+        <v>0.748160202699571</v>
       </c>
       <c r="S159" t="n">
-        <v>0.6823989271851395</v>
+        <v>0.6824043674227691</v>
       </c>
       <c r="T159" t="n">
-        <v>0.6070728003520952</v>
+        <v>0.6070786297433027</v>
       </c>
       <c r="U159" t="n">
-        <v>0.532103027587208</v>
+        <v>0.5321061832962011</v>
       </c>
       <c r="V159" t="n">
         <v>0.4709951443799548</v>
@@ -12534,58 +12534,58 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.06643635012914528</v>
+        <v>0.06643604238390541</v>
       </c>
       <c r="F160" t="n">
-        <v>0.0775365054882849</v>
+        <v>0.0775358465961633</v>
       </c>
       <c r="G160" t="n">
-        <v>0.07757139131147046</v>
+        <v>0.07757052909756382</v>
       </c>
       <c r="H160" t="n">
-        <v>0.08007482663309369</v>
+        <v>0.08007385266171001</v>
       </c>
       <c r="I160" t="n">
-        <v>0.08199643336024906</v>
+        <v>0.08199549929883944</v>
       </c>
       <c r="J160" t="n">
-        <v>0.08473773600101302</v>
+        <v>0.08473685698476999</v>
       </c>
       <c r="K160" t="n">
-        <v>0.08901877445186525</v>
+        <v>0.08901798787421142</v>
       </c>
       <c r="L160" t="n">
-        <v>0.09388730989563057</v>
+        <v>0.09388662891459114</v>
       </c>
       <c r="M160" t="n">
-        <v>0.1002689258531723</v>
+        <v>0.1002683202653462</v>
       </c>
       <c r="N160" t="n">
-        <v>0.1022616943033478</v>
+        <v>0.1022611363397454</v>
       </c>
       <c r="O160" t="n">
-        <v>0.09902254318049117</v>
+        <v>0.09902205140081206</v>
       </c>
       <c r="P160" t="n">
-        <v>0.09339365965275563</v>
+        <v>0.09339320900793924</v>
       </c>
       <c r="Q160" t="n">
-        <v>0.08921074123539156</v>
+        <v>0.08921035265978858</v>
       </c>
       <c r="R160" t="n">
-        <v>0.08615548266914855</v>
+        <v>0.08615510926504269</v>
       </c>
       <c r="S160" t="n">
-        <v>0.08236533267519987</v>
+        <v>0.08236499689281371</v>
       </c>
       <c r="T160" t="n">
-        <v>0.07679777434066827</v>
+        <v>0.07679745185324838</v>
       </c>
       <c r="U160" t="n">
-        <v>0.07023726318332406</v>
+        <v>0.0702369792768955</v>
       </c>
       <c r="V160" t="n">
-        <v>0.06409422015775132</v>
+        <v>0.06409394965579979</v>
       </c>
     </row>
     <row r="161">
@@ -12686,19 +12686,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5.447785902146947</v>
+        <v>5.524367667083248</v>
       </c>
       <c r="F162" t="n">
-        <v>3.686757446958143</v>
+        <v>3.768178401733558</v>
       </c>
       <c r="G162" t="n">
-        <v>2.371379665789518</v>
+        <v>2.43599676516434</v>
       </c>
       <c r="H162" t="n">
-        <v>1.661362870466969</v>
+        <v>1.716575489802384</v>
       </c>
       <c r="I162" t="n">
-        <v>1.202588466322946</v>
+        <v>1.262138447937285</v>
       </c>
       <c r="J162" t="n">
         <v>0.3801709747006228</v>
@@ -12762,19 +12762,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.6025466054118475</v>
+        <v>0.6021440694351945</v>
       </c>
       <c r="F163" t="n">
-        <v>0.7104033302786456</v>
+        <v>0.7111703467851084</v>
       </c>
       <c r="G163" t="n">
-        <v>0.7808386708722137</v>
+        <v>0.7856805348175046</v>
       </c>
       <c r="H163" t="n">
-        <v>0.7956823136838596</v>
+        <v>0.8049356172765622</v>
       </c>
       <c r="I163" t="n">
-        <v>0.7343512332248686</v>
+        <v>0.7499844268338677</v>
       </c>
       <c r="J163" t="n">
         <v>0.4664774124429842</v>
@@ -12838,19 +12838,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.2252385224506654</v>
+        <v>0.211862238938862</v>
       </c>
       <c r="F164" t="n">
-        <v>0.3001203596306623</v>
+        <v>0.2806454537982108</v>
       </c>
       <c r="G164" t="n">
-        <v>0.3470610690422596</v>
+        <v>0.3272518994606054</v>
       </c>
       <c r="H164" t="n">
-        <v>0.3784114019714675</v>
+        <v>0.3578598831983368</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3972999991892638</v>
+        <v>0.3723288894598689</v>
       </c>
       <c r="J164" t="n">
         <v>0.6315223547316684</v>
@@ -12914,19 +12914,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.4603823167966015</v>
+        <v>0.4550094366683314</v>
       </c>
       <c r="F165" t="n">
-        <v>0.5321986904814981</v>
+        <v>0.5229376396606431</v>
       </c>
       <c r="G165" t="n">
-        <v>0.5138668306497182</v>
+        <v>0.4986793692564479</v>
       </c>
       <c r="H165" t="n">
-        <v>0.4943220299364402</v>
+        <v>0.4712042195180869</v>
       </c>
       <c r="I165" t="n">
-        <v>0.4909679416859084</v>
+        <v>0.4539445800379098</v>
       </c>
       <c r="J165" t="n">
         <v>0.9138212090218202</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.1932214308480643</v>
+        <v>0.170433634900009</v>
       </c>
       <c r="F166" t="n">
-        <v>0.2579000617347089</v>
+        <v>0.2161634162621433</v>
       </c>
       <c r="G166" t="n">
-        <v>0.2956892924251108</v>
+        <v>0.2400424253123456</v>
       </c>
       <c r="H166" t="n">
-        <v>0.3412341551199829</v>
+        <v>0.2681534118981959</v>
       </c>
       <c r="I166" t="n">
-        <v>0.4460119338331411</v>
+        <v>0.3368973679652041</v>
       </c>
       <c r="J166" t="n">
         <v>1.773857294590268</v>
@@ -13066,19 +13066,19 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>2.634567712944311</v>
+        <v>2.668288607023222</v>
       </c>
       <c r="F167" t="n">
-        <v>2.5512778947045</v>
+        <v>2.602220914691288</v>
       </c>
       <c r="G167" t="n">
-        <v>2.288035965078569</v>
+        <v>2.346177392738553</v>
       </c>
       <c r="H167" t="n">
-        <v>2.044028534699716</v>
+        <v>2.112670643437423</v>
       </c>
       <c r="I167" t="n">
-        <v>1.709647832891055</v>
+        <v>1.805360270845356</v>
       </c>
       <c r="J167" t="n">
         <v>0.3582294050350698</v>
@@ -13142,19 +13142,19 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5.305723890748298</v>
+        <v>5.374564027294393</v>
       </c>
       <c r="F168" t="n">
-        <v>5.694454778403223</v>
+        <v>5.813202974789389</v>
       </c>
       <c r="G168" t="n">
-        <v>5.534850265496048</v>
+        <v>5.686559941534906</v>
       </c>
       <c r="H168" t="n">
-        <v>5.171434771942405</v>
+        <v>5.363722141495725</v>
       </c>
       <c r="I168" t="n">
-        <v>4.386192806259841</v>
+        <v>4.664391862689689</v>
       </c>
       <c r="J168" t="n">
         <v>0.4966535260621989</v>
@@ -13218,19 +13218,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.3904899951496454</v>
+        <v>0.3828263254985528</v>
       </c>
       <c r="F169" t="n">
-        <v>0.4417096770898813</v>
+        <v>0.4270052470456932</v>
       </c>
       <c r="G169" t="n">
-        <v>0.4502158113794165</v>
+        <v>0.4299783434587163</v>
       </c>
       <c r="H169" t="n">
-        <v>0.4607192894492997</v>
+        <v>0.4352300827251504</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4759093699052087</v>
+        <v>0.4411556517144274</v>
       </c>
       <c r="J169" t="n">
         <v>0.8248679234959864</v>
@@ -13294,19 +13294,19 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.2825084911046173</v>
+        <v>0.2747872208692231</v>
       </c>
       <c r="F170" t="n">
-        <v>0.3662813935067979</v>
+        <v>0.3558467593725703</v>
       </c>
       <c r="G170" t="n">
-        <v>0.4064525740298927</v>
+        <v>0.3959409285412541</v>
       </c>
       <c r="H170" t="n">
-        <v>0.4186083217821607</v>
+        <v>0.4068507050624116</v>
       </c>
       <c r="I170" t="n">
-        <v>0.4102989224736578</v>
+        <v>0.3937973900806679</v>
       </c>
       <c r="J170" t="n">
         <v>0.5773156239790919</v>
@@ -13370,19 +13370,19 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.43659168716966</v>
+        <v>0.4356899987708279</v>
       </c>
       <c r="F171" t="n">
-        <v>0.4816941239308597</v>
+        <v>0.4795084716529281</v>
       </c>
       <c r="G171" t="n">
-        <v>0.4798793598790521</v>
+        <v>0.4764834221425793</v>
       </c>
       <c r="H171" t="n">
-        <v>0.4652337272393027</v>
+        <v>0.4602674948393882</v>
       </c>
       <c r="I171" t="n">
-        <v>0.4352416059584863</v>
+        <v>0.4271783925296114</v>
       </c>
       <c r="J171" t="n">
         <v>0.496652316764546</v>
@@ -13446,19 +13446,19 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3.173449363739302</v>
+        <v>3.217839910516098</v>
       </c>
       <c r="F172" t="n">
-        <v>3.093921065060034</v>
+        <v>3.163534626805775</v>
       </c>
       <c r="G172" t="n">
-        <v>2.615022962792515</v>
+        <v>2.691931127961233</v>
       </c>
       <c r="H172" t="n">
-        <v>2.126100234651466</v>
+        <v>2.210111863860671</v>
       </c>
       <c r="I172" t="n">
-        <v>1.616357289553709</v>
+        <v>1.724368382442782</v>
       </c>
       <c r="J172" t="n">
         <v>0.1230010054856119</v>
@@ -13522,19 +13522,19 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>0.2181777290678178</v>
+        <v>0.2054003158687986</v>
       </c>
       <c r="F173" t="n">
-        <v>0.2860393833870454</v>
+        <v>0.2667092037733401</v>
       </c>
       <c r="G173" t="n">
-        <v>0.3187558705428963</v>
+        <v>0.2967078788998079</v>
       </c>
       <c r="H173" t="n">
-        <v>0.3363692354650054</v>
+        <v>0.3095502831510157</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3589468494998898</v>
+        <v>0.320685494856194</v>
       </c>
       <c r="J173" t="n">
         <v>0.7898853212439433</v>
@@ -13598,19 +13598,19 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1.263198544342022</v>
+        <v>1.275988491588088</v>
       </c>
       <c r="F174" t="n">
-        <v>1.294862600014543</v>
+        <v>1.314508927522271</v>
       </c>
       <c r="G174" t="n">
-        <v>1.209885057000394</v>
+        <v>1.232286590757177</v>
       </c>
       <c r="H174" t="n">
-        <v>1.110334728795247</v>
+        <v>1.136441311252318</v>
       </c>
       <c r="I174" t="n">
-        <v>0.9582071926634452</v>
+        <v>0.9941436900651047</v>
       </c>
       <c r="J174" t="n">
         <v>0.4171414422283697</v>
@@ -13674,19 +13674,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>0.2395584358381428</v>
+        <v>0.219106864097731</v>
       </c>
       <c r="F175" t="n">
-        <v>0.3461850183772864</v>
+        <v>0.3206534775308436</v>
       </c>
       <c r="G175" t="n">
-        <v>0.4221379919474748</v>
+        <v>0.3996046588916712</v>
       </c>
       <c r="H175" t="n">
-        <v>0.477823551722735</v>
+        <v>0.4579051048812466</v>
       </c>
       <c r="I175" t="n">
-        <v>0.5057761458581214</v>
+        <v>0.4860790458293018</v>
       </c>
       <c r="J175" t="n">
         <v>0.6384347283320547</v>
@@ -13750,19 +13750,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>0.4192056119063418</v>
+        <v>0.4196037539103232</v>
       </c>
       <c r="F176" t="n">
-        <v>0.4199001044106442</v>
+        <v>0.4181411142779204</v>
       </c>
       <c r="G176" t="n">
-        <v>0.3970267591674926</v>
+        <v>0.3926754448062674</v>
       </c>
       <c r="H176" t="n">
-        <v>0.3774517300707322</v>
+        <v>0.3702733702924871</v>
       </c>
       <c r="I176" t="n">
-        <v>0.35680536206611</v>
+        <v>0.3450368739466326</v>
       </c>
       <c r="J176" t="n">
         <v>0.473428068913139</v>
@@ -13826,19 +13826,19 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>0.7176779914089261</v>
+        <v>0.7176657786717366</v>
       </c>
       <c r="F177" t="n">
-        <v>0.9676857698949254</v>
+        <v>0.9744947667973989</v>
       </c>
       <c r="G177" t="n">
-        <v>1.108956778853178</v>
+        <v>1.124756083481395</v>
       </c>
       <c r="H177" t="n">
-        <v>1.131568212682158</v>
+        <v>1.156163690900293</v>
       </c>
       <c r="I177" t="n">
-        <v>1.011138548228371</v>
+        <v>1.04822353546505</v>
       </c>
       <c r="J177" t="n">
         <v>0.4585840931334159</v>
@@ -13902,19 +13902,19 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>0.2062011576603314</v>
+        <v>0.2031425449623628</v>
       </c>
       <c r="F178" t="n">
-        <v>0.2399724529404399</v>
+        <v>0.2347134688426061</v>
       </c>
       <c r="G178" t="n">
-        <v>0.2450666796298997</v>
+        <v>0.2380568113687554</v>
       </c>
       <c r="H178" t="n">
-        <v>0.2422401602819594</v>
+        <v>0.2326898232561549</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2384187447582178</v>
+        <v>0.2235052396056729</v>
       </c>
       <c r="J178" t="n">
         <v>0.4073984384785604</v>
@@ -13978,19 +13978,19 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>0.5845150729777657</v>
+        <v>0.5866757604692402</v>
       </c>
       <c r="F179" t="n">
-        <v>0.6348936495875539</v>
+        <v>0.637960346137657</v>
       </c>
       <c r="G179" t="n">
-        <v>0.6407426685567467</v>
+        <v>0.6449455125365465</v>
       </c>
       <c r="H179" t="n">
-        <v>0.6223027498483018</v>
+        <v>0.6278716321588776</v>
       </c>
       <c r="I179" t="n">
-        <v>0.5642035413765258</v>
+        <v>0.5721968003557761</v>
       </c>
       <c r="J179" t="n">
         <v>0.4051493481222028</v>
